--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_retail_automotive.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08126027036669453</v>
+        <v>0.08109086969077779</v>
       </c>
       <c r="C2">
-        <v>13317.63560765907</v>
+        <v>13237.84200523092</v>
       </c>
       <c r="D2">
-        <v>12439.33560765907</v>
+        <v>12499.04600523092</v>
       </c>
       <c r="E2">
-        <v>-1971.1</v>
+        <v>-1831.596</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>139.504</v>
       </c>
       <c r="G2">
         <v>878.3</v>
@@ -1457,28 +1457,28 @@
         <v>839.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>7.017051199999999</v>
       </c>
       <c r="N2">
-        <v>839.6</v>
+        <v>832.5829488000001</v>
       </c>
       <c r="O2">
-        <v>209.9</v>
+        <v>208.1457372</v>
       </c>
       <c r="P2">
-        <v>629.7</v>
+        <v>624.4372116000001</v>
       </c>
       <c r="Q2">
-        <v>801.5</v>
+        <v>796.2372116</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08126027036669453</v>
+        <v>0.08152890877856343</v>
       </c>
       <c r="T2">
-        <v>0.7107536019307608</v>
+        <v>0.7161380989150847</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>119.6514000068861</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08109086969077779</v>
+        <v>0.08092146901486107</v>
       </c>
       <c r="C3">
-        <v>13237.84200523092</v>
+        <v>13158.62440272484</v>
       </c>
       <c r="D3">
-        <v>12499.04600523092</v>
+        <v>12559.33240272484</v>
       </c>
       <c r="E3">
-        <v>-1831.596</v>
+        <v>-1692.092</v>
       </c>
       <c r="F3">
-        <v>139.504</v>
+        <v>279.008</v>
       </c>
       <c r="G3">
         <v>878.3</v>
@@ -1539,28 +1539,28 @@
         <v>839.6</v>
       </c>
       <c r="M3">
-        <v>7.017051199999999</v>
+        <v>14.0341024</v>
       </c>
       <c r="N3">
-        <v>832.5829488000001</v>
+        <v>825.5658976</v>
       </c>
       <c r="O3">
-        <v>208.1457372</v>
+        <v>206.3914744</v>
       </c>
       <c r="P3">
-        <v>624.4372116000001</v>
+        <v>619.1744232</v>
       </c>
       <c r="Q3">
-        <v>796.2372116</v>
+        <v>790.9744231999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08152890877856343</v>
+        <v>0.08180302960700109</v>
       </c>
       <c r="T3">
-        <v>0.7161380989150847</v>
+        <v>0.7216324835929663</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>119.6514000068861</v>
+        <v>59.82570000344305</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08092146901486107</v>
+        <v>0.08075206833894431</v>
       </c>
       <c r="C4">
-        <v>13158.62440272484</v>
+        <v>13079.99117516248</v>
       </c>
       <c r="D4">
-        <v>12559.33240272484</v>
+        <v>12620.20317516248</v>
       </c>
       <c r="E4">
-        <v>-1692.092</v>
+        <v>-1552.588</v>
       </c>
       <c r="F4">
-        <v>279.008</v>
+        <v>418.512</v>
       </c>
       <c r="G4">
         <v>878.3</v>
@@ -1621,28 +1621,28 @@
         <v>839.6</v>
       </c>
       <c r="M4">
-        <v>14.0341024</v>
+        <v>21.0511536</v>
       </c>
       <c r="N4">
-        <v>825.5658976</v>
+        <v>818.5488464</v>
       </c>
       <c r="O4">
-        <v>206.3914744</v>
+        <v>204.6372116</v>
       </c>
       <c r="P4">
-        <v>619.1744232</v>
+        <v>613.9116348</v>
       </c>
       <c r="Q4">
-        <v>790.9744231999999</v>
+        <v>785.7116348</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08180302960700109</v>
+        <v>0.0820828024112828</v>
       </c>
       <c r="T4">
-        <v>0.7216324835929663</v>
+        <v>0.7272401545528659</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.82570000344305</v>
+        <v>39.88380000229536</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08075206833894431</v>
+        <v>0.08058266766302759</v>
       </c>
       <c r="C5">
-        <v>13079.99117516248</v>
+        <v>13001.95086071963</v>
       </c>
       <c r="D5">
-        <v>12620.20317516248</v>
+        <v>12681.66686071963</v>
       </c>
       <c r="E5">
-        <v>-1552.588</v>
+        <v>-1413.084</v>
       </c>
       <c r="F5">
-        <v>418.512</v>
+        <v>558.016</v>
       </c>
       <c r="G5">
         <v>878.3</v>
@@ -1703,28 +1703,28 @@
         <v>839.6</v>
       </c>
       <c r="M5">
-        <v>21.0511536</v>
+        <v>28.0682048</v>
       </c>
       <c r="N5">
-        <v>818.5488464</v>
+        <v>811.5317952</v>
       </c>
       <c r="O5">
-        <v>204.6372116</v>
+        <v>202.8829488</v>
       </c>
       <c r="P5">
-        <v>613.9116348</v>
+        <v>608.6488464</v>
       </c>
       <c r="Q5">
-        <v>785.7116348</v>
+        <v>780.4488464</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0820828024112828</v>
+        <v>0.08236840381565375</v>
       </c>
       <c r="T5">
-        <v>0.7272401545528659</v>
+        <v>0.7329646519910971</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.88380000229536</v>
+        <v>29.91285000172153</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08058266766302759</v>
+        <v>0.08041326698711086</v>
       </c>
       <c r="C6">
-        <v>13001.95086071963</v>
+        <v>12924.51216471871</v>
       </c>
       <c r="D6">
-        <v>12681.66686071963</v>
+        <v>12743.73216471871</v>
       </c>
       <c r="E6">
-        <v>-1413.084</v>
+        <v>-1273.58</v>
       </c>
       <c r="F6">
-        <v>558.016</v>
+        <v>697.52</v>
       </c>
       <c r="G6">
         <v>878.3</v>
@@ -1785,28 +1785,28 @@
         <v>839.6</v>
       </c>
       <c r="M6">
-        <v>28.0682048</v>
+        <v>35.08525599999999</v>
       </c>
       <c r="N6">
-        <v>811.5317952</v>
+        <v>804.5147440000001</v>
       </c>
       <c r="O6">
-        <v>202.8829488</v>
+        <v>201.128686</v>
       </c>
       <c r="P6">
-        <v>608.6488464</v>
+        <v>603.386058</v>
       </c>
       <c r="Q6">
-        <v>780.4488464</v>
+        <v>775.186058</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08236840381565375</v>
+        <v>0.08266001788116932</v>
       </c>
       <c r="T6">
-        <v>0.7329646519910971</v>
+        <v>0.7388096651648698</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.91285000172153</v>
+        <v>23.93028000137722</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08041326698711086</v>
+        <v>0.08024386631119411</v>
       </c>
       <c r="C7">
-        <v>12924.51216471871</v>
+        <v>12847.6839637391</v>
       </c>
       <c r="D7">
-        <v>12743.73216471871</v>
+        <v>12806.4079637391</v>
       </c>
       <c r="E7">
-        <v>-1273.58</v>
+        <v>-1134.076</v>
       </c>
       <c r="F7">
-        <v>697.52</v>
+        <v>837.024</v>
       </c>
       <c r="G7">
         <v>878.3</v>
@@ -1867,28 +1867,28 @@
         <v>839.6</v>
       </c>
       <c r="M7">
-        <v>35.08525599999999</v>
+        <v>42.1023072</v>
       </c>
       <c r="N7">
-        <v>804.5147440000001</v>
+        <v>797.4976928</v>
       </c>
       <c r="O7">
-        <v>201.128686</v>
+        <v>199.3744232</v>
       </c>
       <c r="P7">
-        <v>603.386058</v>
+        <v>598.1232696</v>
       </c>
       <c r="Q7">
-        <v>775.186058</v>
+        <v>769.9232695999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08266001788116932</v>
+        <v>0.08295783650127034</v>
       </c>
       <c r="T7">
-        <v>0.7388096651648698</v>
+        <v>0.7447790403210631</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.93028000137722</v>
+        <v>19.94190000114768</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08024386631119411</v>
+        <v>0.08007446563527738</v>
       </c>
       <c r="C8">
-        <v>12847.6839637391</v>
+        <v>12771.47530984917</v>
       </c>
       <c r="D8">
-        <v>12806.4079637391</v>
+        <v>12869.70330984917</v>
       </c>
       <c r="E8">
-        <v>-1134.076</v>
+        <v>-994.572</v>
       </c>
       <c r="F8">
-        <v>837.024</v>
+        <v>976.5279999999999</v>
       </c>
       <c r="G8">
         <v>878.3</v>
@@ -1949,28 +1949,28 @@
         <v>839.6</v>
       </c>
       <c r="M8">
-        <v>42.1023072</v>
+        <v>49.1193584</v>
       </c>
       <c r="N8">
-        <v>797.4976928</v>
+        <v>790.4806416</v>
       </c>
       <c r="O8">
-        <v>199.3744232</v>
+        <v>197.6201604</v>
       </c>
       <c r="P8">
-        <v>598.1232696</v>
+        <v>592.8604812</v>
       </c>
       <c r="Q8">
-        <v>769.9232695999999</v>
+        <v>764.6604811999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08295783650127034</v>
+        <v>0.0832620598228789</v>
       </c>
       <c r="T8">
-        <v>0.7447790403210631</v>
+        <v>0.7508767891365294</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.94190000114768</v>
+        <v>17.09305714384087</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08007446563527737</v>
+        <v>0.07990506495936064</v>
       </c>
       <c r="C9">
-        <v>12771.47530984918</v>
+        <v>12695.89543496473</v>
       </c>
       <c r="D9">
-        <v>12869.70330984918</v>
+        <v>12933.62743496473</v>
       </c>
       <c r="E9">
-        <v>-994.5719999999999</v>
+        <v>-855.068</v>
       </c>
       <c r="F9">
-        <v>976.528</v>
+        <v>1116.032</v>
       </c>
       <c r="G9">
         <v>878.3</v>
@@ -2031,28 +2031,28 @@
         <v>839.6</v>
       </c>
       <c r="M9">
-        <v>49.1193584</v>
+        <v>56.13640959999999</v>
       </c>
       <c r="N9">
-        <v>790.4806416</v>
+        <v>783.4635904</v>
       </c>
       <c r="O9">
-        <v>197.6201604</v>
+        <v>195.8658976</v>
       </c>
       <c r="P9">
-        <v>592.8604812</v>
+        <v>587.5976928</v>
       </c>
       <c r="Q9">
-        <v>764.6604811999999</v>
+        <v>759.3976928</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0832620598228789</v>
+        <v>0.08357289669495722</v>
       </c>
       <c r="T9">
-        <v>0.7508767891365294</v>
+        <v>0.7571070977088539</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.09305714384087</v>
+        <v>14.95642500086076</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07990506495936064</v>
+        <v>0.07973566428344392</v>
       </c>
       <c r="C10">
-        <v>12695.89543496473</v>
+        <v>12620.95375533772</v>
       </c>
       <c r="D10">
-        <v>12933.62743496473</v>
+        <v>12998.18975533773</v>
       </c>
       <c r="E10">
-        <v>-855.068</v>
+        <v>-715.5640000000001</v>
       </c>
       <c r="F10">
-        <v>1116.032</v>
+        <v>1255.536</v>
       </c>
       <c r="G10">
         <v>878.3</v>
@@ -2113,28 +2113,28 @@
         <v>839.6</v>
       </c>
       <c r="M10">
-        <v>56.13640959999999</v>
+        <v>63.15346079999999</v>
       </c>
       <c r="N10">
-        <v>783.4635904</v>
+        <v>776.4465392000001</v>
       </c>
       <c r="O10">
-        <v>195.8658976</v>
+        <v>194.1116348</v>
       </c>
       <c r="P10">
-        <v>587.5976928</v>
+        <v>582.3349044</v>
       </c>
       <c r="Q10">
-        <v>759.3976928</v>
+        <v>754.1349044</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08357289669495722</v>
+        <v>0.08389056514664166</v>
       </c>
       <c r="T10">
-        <v>0.7571070977088539</v>
+        <v>0.7634743361399106</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.95642500086076</v>
+        <v>13.29460000076512</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07973566428344392</v>
+        <v>0.07956626360752717</v>
       </c>
       <c r="C11">
-        <v>12620.95375533772</v>
+        <v>12546.65987618028</v>
       </c>
       <c r="D11">
-        <v>12998.18975533773</v>
+        <v>13063.39987618028</v>
       </c>
       <c r="E11">
-        <v>-715.5640000000001</v>
+        <v>-576.0600000000002</v>
       </c>
       <c r="F11">
-        <v>1255.536</v>
+        <v>1395.04</v>
       </c>
       <c r="G11">
         <v>878.3</v>
@@ -2195,28 +2195,28 @@
         <v>839.6</v>
       </c>
       <c r="M11">
-        <v>63.15346079999999</v>
+        <v>70.17051199999999</v>
       </c>
       <c r="N11">
-        <v>776.4465392000001</v>
+        <v>769.429488</v>
       </c>
       <c r="O11">
-        <v>194.1116348</v>
+        <v>192.357372</v>
       </c>
       <c r="P11">
-        <v>582.3349044</v>
+        <v>577.0721160000001</v>
       </c>
       <c r="Q11">
-        <v>754.1349044</v>
+        <v>748.872116</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08389056514664166</v>
+        <v>0.08421529289725241</v>
       </c>
       <c r="T11">
-        <v>0.7634743361399106</v>
+        <v>0.7699830687583241</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.29460000076512</v>
+        <v>11.96514000068861</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07956626360752717</v>
+        <v>0.07939686293161043</v>
       </c>
       <c r="C12">
-        <v>12546.65987618028</v>
+        <v>12473.02359642846</v>
       </c>
       <c r="D12">
-        <v>13063.39987618028</v>
+        <v>13129.26759642846</v>
       </c>
       <c r="E12">
-        <v>-576.0599999999999</v>
+        <v>-436.556</v>
       </c>
       <c r="F12">
-        <v>1395.04</v>
+        <v>1534.544</v>
       </c>
       <c r="G12">
         <v>878.3</v>
@@ -2277,28 +2277,28 @@
         <v>839.6</v>
       </c>
       <c r="M12">
-        <v>70.17051199999999</v>
+        <v>77.18756319999999</v>
       </c>
       <c r="N12">
-        <v>769.429488</v>
+        <v>762.4124368</v>
       </c>
       <c r="O12">
-        <v>192.357372</v>
+        <v>190.6031092</v>
       </c>
       <c r="P12">
-        <v>577.0721160000001</v>
+        <v>571.8093276</v>
       </c>
       <c r="Q12">
-        <v>748.872116</v>
+        <v>743.6093275999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08421529289725241</v>
+        <v>0.08454731790068588</v>
       </c>
       <c r="T12">
-        <v>0.7699830687583241</v>
+        <v>0.7766380650310841</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.96514000068861</v>
+        <v>10.87740000062601</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07939686293161043</v>
+        <v>0.0792274622556937</v>
       </c>
       <c r="C13">
-        <v>12473.02359642846</v>
+        <v>12400.05491365098</v>
       </c>
       <c r="D13">
-        <v>13129.26759642846</v>
+        <v>13195.80291365098</v>
       </c>
       <c r="E13">
-        <v>-436.556</v>
+        <v>-297.0519999999999</v>
       </c>
       <c r="F13">
-        <v>1534.544</v>
+        <v>1674.048</v>
       </c>
       <c r="G13">
         <v>878.3</v>
@@ -2359,28 +2359,28 @@
         <v>839.6</v>
       </c>
       <c r="M13">
-        <v>77.18756319999999</v>
+        <v>84.2046144</v>
       </c>
       <c r="N13">
-        <v>762.4124368</v>
+        <v>755.3953856000001</v>
       </c>
       <c r="O13">
-        <v>190.6031092</v>
+        <v>188.8488464</v>
       </c>
       <c r="P13">
-        <v>571.8093276</v>
+        <v>566.5465392000001</v>
       </c>
       <c r="Q13">
-        <v>743.6093275999999</v>
+        <v>738.3465392000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08454731790068588</v>
+        <v>0.08488688892692466</v>
       </c>
       <c r="T13">
-        <v>0.7766380650310841</v>
+        <v>0.783444311219134</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.87740000062601</v>
+        <v>9.970950000573842</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0792274622556937</v>
+        <v>0.07905806157977696</v>
       </c>
       <c r="C14">
-        <v>12400.05491365098</v>
+        <v>12327.76402910795</v>
       </c>
       <c r="D14">
-        <v>13195.80291365098</v>
+        <v>13263.01602910795</v>
       </c>
       <c r="E14">
-        <v>-297.0519999999999</v>
+        <v>-157.548</v>
       </c>
       <c r="F14">
-        <v>1674.048</v>
+        <v>1813.552</v>
       </c>
       <c r="G14">
         <v>878.3</v>
@@ -2441,28 +2441,28 @@
         <v>839.6</v>
       </c>
       <c r="M14">
-        <v>84.2046144</v>
+        <v>91.22166559999999</v>
       </c>
       <c r="N14">
-        <v>755.3953856000001</v>
+        <v>748.3783344000001</v>
       </c>
       <c r="O14">
-        <v>188.8488464</v>
+        <v>187.0945836</v>
       </c>
       <c r="P14">
-        <v>566.5465392000001</v>
+        <v>561.2837508</v>
       </c>
       <c r="Q14">
-        <v>738.3465392000001</v>
+        <v>733.0837508</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08488688892692466</v>
+        <v>0.08523426618365168</v>
       </c>
       <c r="T14">
-        <v>0.783444311219134</v>
+        <v>0.7904070228367942</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.970950000573842</v>
+        <v>9.203953846683547</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07905806157977696</v>
+        <v>0.07904616090386023</v>
       </c>
       <c r="C15">
-        <v>12327.76402910795</v>
+        <v>12193.00761051734</v>
       </c>
       <c r="D15">
-        <v>13263.01602910795</v>
+        <v>13267.76361051734</v>
       </c>
       <c r="E15">
-        <v>-157.548</v>
+        <v>-18.04399999999987</v>
       </c>
       <c r="F15">
-        <v>1813.552</v>
+        <v>1953.056</v>
       </c>
       <c r="G15">
         <v>878.3</v>
@@ -2523,45 +2523,45 @@
         <v>839.6</v>
       </c>
       <c r="M15">
-        <v>91.22166559999999</v>
+        <v>101.1683008</v>
       </c>
       <c r="N15">
-        <v>748.3783344000001</v>
+        <v>738.4316992</v>
       </c>
       <c r="O15">
-        <v>187.0945836</v>
+        <v>184.6079248</v>
       </c>
       <c r="P15">
-        <v>561.2837508</v>
+        <v>553.8237744</v>
       </c>
       <c r="Q15">
-        <v>733.0837508</v>
+        <v>725.6237744</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08523426618365168</v>
+        <v>0.08558972198123282</v>
       </c>
       <c r="T15">
-        <v>0.7904070228367942</v>
+        <v>0.7975316579804467</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.203953846683547</v>
+        <v>8.2990422233127</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07904616090386023</v>
+        <v>0.07888801022794349</v>
       </c>
       <c r="C16">
-        <v>12193.00761051734</v>
+        <v>12116.91950553344</v>
       </c>
       <c r="D16">
-        <v>13267.76361051734</v>
+        <v>13331.17950553344</v>
       </c>
       <c r="E16">
-        <v>-18.04399999999987</v>
+        <v>121.4600000000005</v>
       </c>
       <c r="F16">
-        <v>1953.056</v>
+        <v>2092.56</v>
       </c>
       <c r="G16">
         <v>878.3</v>
@@ -2605,28 +2605,28 @@
         <v>839.6</v>
       </c>
       <c r="M16">
-        <v>101.1683008</v>
+        <v>108.394608</v>
       </c>
       <c r="N16">
-        <v>738.4316992</v>
+        <v>731.205392</v>
       </c>
       <c r="O16">
-        <v>184.6079248</v>
+        <v>182.801348</v>
       </c>
       <c r="P16">
-        <v>553.8237744</v>
+        <v>548.404044</v>
       </c>
       <c r="Q16">
-        <v>725.6237744</v>
+        <v>720.204044</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08558972198123282</v>
+        <v>0.0859535414446394</v>
       </c>
       <c r="T16">
-        <v>0.7975316579804467</v>
+        <v>0.8048239315980673</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.2990422233127</v>
+        <v>7.745772741758518</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07888801022794349</v>
+        <v>0.07872985955202674</v>
       </c>
       <c r="C17">
-        <v>12116.91950553344</v>
+        <v>12041.44052957694</v>
       </c>
       <c r="D17">
-        <v>13331.17950553344</v>
+        <v>13395.20452957694</v>
       </c>
       <c r="E17">
-        <v>121.46</v>
+        <v>260.9639999999999</v>
       </c>
       <c r="F17">
-        <v>2092.56</v>
+        <v>2232.064</v>
       </c>
       <c r="G17">
         <v>878.3</v>
@@ -2687,28 +2687,28 @@
         <v>839.6</v>
       </c>
       <c r="M17">
-        <v>108.394608</v>
+        <v>115.6209152</v>
       </c>
       <c r="N17">
-        <v>731.2053920000001</v>
+        <v>723.9790848</v>
       </c>
       <c r="O17">
-        <v>182.801348</v>
+        <v>180.9947712</v>
       </c>
       <c r="P17">
-        <v>548.4040440000001</v>
+        <v>542.9843136</v>
       </c>
       <c r="Q17">
-        <v>720.2040440000001</v>
+        <v>714.7843135999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0859535414446394</v>
+        <v>0.08632602327622232</v>
       </c>
       <c r="T17">
-        <v>0.8048239315980673</v>
+        <v>0.8122898307780122</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.745772741758521</v>
+        <v>7.261661945398614</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07872985955202674</v>
+        <v>0.07857170887611002</v>
       </c>
       <c r="C18">
-        <v>12041.44052957694</v>
+        <v>11966.57950130612</v>
       </c>
       <c r="D18">
-        <v>13395.20452957694</v>
+        <v>13459.84750130612</v>
       </c>
       <c r="E18">
-        <v>260.9639999999999</v>
+        <v>400.4680000000003</v>
       </c>
       <c r="F18">
-        <v>2232.064</v>
+        <v>2371.568</v>
       </c>
       <c r="G18">
         <v>878.3</v>
@@ -2769,28 +2769,28 @@
         <v>839.6</v>
       </c>
       <c r="M18">
-        <v>115.6209152</v>
+        <v>122.8472224</v>
       </c>
       <c r="N18">
-        <v>723.9790848</v>
+        <v>716.7527776000001</v>
       </c>
       <c r="O18">
-        <v>180.9947712</v>
+        <v>179.1881944</v>
       </c>
       <c r="P18">
-        <v>542.9843136</v>
+        <v>537.5645832</v>
       </c>
       <c r="Q18">
-        <v>714.7843135999999</v>
+        <v>709.3645832</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08632602327622232</v>
+        <v>0.08670748057362654</v>
       </c>
       <c r="T18">
-        <v>0.8122898307780122</v>
+        <v>0.8199356311430163</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.261661945398614</v>
+        <v>6.834505360375164</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07857170887611002</v>
+        <v>0.07864305820019328</v>
       </c>
       <c r="C19">
-        <v>11966.57950130612</v>
+        <v>11797.83489235831</v>
       </c>
       <c r="D19">
-        <v>13459.84750130612</v>
+        <v>13430.60689235831</v>
       </c>
       <c r="E19">
-        <v>400.4680000000003</v>
+        <v>539.9720000000002</v>
       </c>
       <c r="F19">
-        <v>2371.568</v>
+        <v>2511.072</v>
       </c>
       <c r="G19">
         <v>878.3</v>
@@ -2851,45 +2851,45 @@
         <v>839.6</v>
       </c>
       <c r="M19">
-        <v>122.8472224</v>
+        <v>134.342352</v>
       </c>
       <c r="N19">
-        <v>716.7527776000001</v>
+        <v>705.257648</v>
       </c>
       <c r="O19">
-        <v>179.1881944</v>
+        <v>176.314412</v>
       </c>
       <c r="P19">
-        <v>537.5645832</v>
+        <v>528.9432360000001</v>
       </c>
       <c r="Q19">
-        <v>709.3645832</v>
+        <v>700.743236</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08670748057362654</v>
+        <v>0.08709824170755277</v>
       </c>
       <c r="T19">
-        <v>0.8199356311430163</v>
+        <v>0.8277679144437518</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.834505360375164</v>
+        <v>6.249704486340987</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07864305820019327</v>
+        <v>0.07849765752427657</v>
       </c>
       <c r="C20">
-        <v>11797.83489235832</v>
+        <v>11718.05441593705</v>
       </c>
       <c r="D20">
-        <v>13430.60689235832</v>
+        <v>13490.33041593705</v>
       </c>
       <c r="E20">
-        <v>539.9719999999998</v>
+        <v>679.4760000000001</v>
       </c>
       <c r="F20">
-        <v>2511.072</v>
+        <v>2650.576</v>
       </c>
       <c r="G20">
         <v>878.3</v>
@@ -2933,28 +2933,28 @@
         <v>839.6</v>
       </c>
       <c r="M20">
-        <v>134.342352</v>
+        <v>141.805816</v>
       </c>
       <c r="N20">
-        <v>705.257648</v>
+        <v>697.7941840000001</v>
       </c>
       <c r="O20">
-        <v>176.314412</v>
+        <v>174.448546</v>
       </c>
       <c r="P20">
-        <v>528.9432360000001</v>
+        <v>523.345638</v>
       </c>
       <c r="Q20">
-        <v>700.743236</v>
+        <v>695.145638</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08709824170755277</v>
+        <v>0.08749865126453896</v>
       </c>
       <c r="T20">
-        <v>0.8277679144437518</v>
+        <v>0.8357935874556169</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.249704486340987</v>
+        <v>5.920772671270409</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07849765752427657</v>
+        <v>0.07835225684835982</v>
       </c>
       <c r="C21">
-        <v>11718.05441593705</v>
+        <v>11638.80747184426</v>
       </c>
       <c r="D21">
-        <v>13490.33041593705</v>
+        <v>13550.58747184426</v>
       </c>
       <c r="E21">
-        <v>679.4760000000001</v>
+        <v>818.98</v>
       </c>
       <c r="F21">
-        <v>2650.576</v>
+        <v>2790.08</v>
       </c>
       <c r="G21">
         <v>878.3</v>
@@ -3015,28 +3015,28 @@
         <v>839.6</v>
       </c>
       <c r="M21">
-        <v>141.805816</v>
+        <v>149.26928</v>
       </c>
       <c r="N21">
-        <v>697.7941840000001</v>
+        <v>690.33072</v>
       </c>
       <c r="O21">
-        <v>174.448546</v>
+        <v>172.58268</v>
       </c>
       <c r="P21">
-        <v>523.345638</v>
+        <v>517.7480400000001</v>
       </c>
       <c r="Q21">
-        <v>695.145638</v>
+        <v>689.54804</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08749865126453896</v>
+        <v>0.08790907106044976</v>
       </c>
       <c r="T21">
-        <v>0.8357935874556169</v>
+        <v>0.8440199022927783</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.920772671270409</v>
+        <v>5.624734037706888</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07835225684835982</v>
+        <v>0.07833285617244308</v>
       </c>
       <c r="C22">
-        <v>11638.80747184426</v>
+        <v>11507.38424270032</v>
       </c>
       <c r="D22">
-        <v>13550.58747184426</v>
+        <v>13558.66824270032</v>
       </c>
       <c r="E22">
-        <v>818.98</v>
+        <v>958.4840000000004</v>
       </c>
       <c r="F22">
-        <v>2790.08</v>
+        <v>2929.584</v>
       </c>
       <c r="G22">
         <v>878.3</v>
@@ -3097,45 +3097,45 @@
         <v>839.6</v>
       </c>
       <c r="M22">
-        <v>149.26928</v>
+        <v>159.0764112</v>
       </c>
       <c r="N22">
-        <v>690.33072</v>
+        <v>680.5235888</v>
       </c>
       <c r="O22">
-        <v>172.58268</v>
+        <v>170.1308972</v>
       </c>
       <c r="P22">
-        <v>517.7480400000001</v>
+        <v>510.3926916</v>
       </c>
       <c r="Q22">
-        <v>689.54804</v>
+        <v>682.1926916</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08790907106044976</v>
+        <v>0.0883298812309406</v>
       </c>
       <c r="T22">
-        <v>0.8440199022927783</v>
+        <v>0.8524544782650579</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.624734037706888</v>
+        <v>5.277966693279286</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07833285617244308</v>
+        <v>0.07819345549652633</v>
       </c>
       <c r="C23">
-        <v>11507.38424270032</v>
+        <v>11426.2280629187</v>
       </c>
       <c r="D23">
-        <v>13558.66824270032</v>
+        <v>13617.0160629187</v>
       </c>
       <c r="E23">
-        <v>958.4839999999999</v>
+        <v>1097.988</v>
       </c>
       <c r="F23">
-        <v>2929.584</v>
+        <v>3069.088</v>
       </c>
       <c r="G23">
         <v>878.3</v>
@@ -3179,28 +3179,28 @@
         <v>839.6</v>
       </c>
       <c r="M23">
-        <v>159.0764112</v>
+        <v>166.6514784</v>
       </c>
       <c r="N23">
-        <v>680.5235888</v>
+        <v>672.9485216</v>
       </c>
       <c r="O23">
-        <v>170.1308972</v>
+        <v>168.2371304</v>
       </c>
       <c r="P23">
-        <v>510.3926916</v>
+        <v>504.7113912</v>
       </c>
       <c r="Q23">
-        <v>682.1926916</v>
+        <v>676.5113911999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0883298812309406</v>
+        <v>0.08876148140580299</v>
       </c>
       <c r="T23">
-        <v>0.8524544782650579</v>
+        <v>0.861105325416114</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.277966693279286</v>
+        <v>5.038059116312046</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07819345549652633</v>
+        <v>0.07805405482060959</v>
       </c>
       <c r="C24">
-        <v>11426.2280629187</v>
+        <v>11345.57623681428</v>
       </c>
       <c r="D24">
-        <v>13617.0160629187</v>
+        <v>13675.86823681428</v>
       </c>
       <c r="E24">
-        <v>1097.988</v>
+        <v>1237.492</v>
       </c>
       <c r="F24">
-        <v>3069.088</v>
+        <v>3208.592</v>
       </c>
       <c r="G24">
         <v>878.3</v>
@@ -3261,28 +3261,28 @@
         <v>839.6</v>
       </c>
       <c r="M24">
-        <v>166.6514784</v>
+        <v>174.2265456</v>
       </c>
       <c r="N24">
-        <v>672.9485216</v>
+        <v>665.3734544</v>
       </c>
       <c r="O24">
-        <v>168.2371304</v>
+        <v>166.3433636</v>
       </c>
       <c r="P24">
-        <v>504.7113912</v>
+        <v>499.0300908</v>
       </c>
       <c r="Q24">
-        <v>676.5113911999999</v>
+        <v>670.8300908</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08876148140580299</v>
+        <v>0.08920429197481766</v>
       </c>
       <c r="T24">
-        <v>0.861105325416114</v>
+        <v>0.8699808698957688</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.038059116312046</v>
+        <v>4.819013067776739</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07805405482060959</v>
+        <v>0.07791465414469287</v>
       </c>
       <c r="C25">
-        <v>11345.57623681428</v>
+        <v>11265.43533215918</v>
       </c>
       <c r="D25">
-        <v>13675.86823681428</v>
+        <v>13735.23133215918</v>
       </c>
       <c r="E25">
-        <v>1237.492</v>
+        <v>1376.996</v>
       </c>
       <c r="F25">
-        <v>3208.592</v>
+        <v>3348.096</v>
       </c>
       <c r="G25">
         <v>878.3</v>
@@ -3343,28 +3343,28 @@
         <v>839.6</v>
       </c>
       <c r="M25">
-        <v>174.2265456</v>
+        <v>181.8016128</v>
       </c>
       <c r="N25">
-        <v>665.3734544</v>
+        <v>657.7983872</v>
       </c>
       <c r="O25">
-        <v>166.3433636</v>
+        <v>164.4495968</v>
       </c>
       <c r="P25">
-        <v>499.0300908</v>
+        <v>493.3487904</v>
       </c>
       <c r="Q25">
-        <v>670.8300908</v>
+        <v>665.1487903999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08920429197481766</v>
+        <v>0.08965875545354324</v>
       </c>
       <c r="T25">
-        <v>0.8699808698957688</v>
+        <v>0.8790899813354147</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.819013067776739</v>
+        <v>4.618220856619375</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07791465414469287</v>
+        <v>0.07777525346877612</v>
       </c>
       <c r="C26">
-        <v>11265.43533215918</v>
+        <v>11185.81203125811</v>
       </c>
       <c r="D26">
-        <v>13735.23133215918</v>
+        <v>13795.11203125811</v>
       </c>
       <c r="E26">
-        <v>1376.996</v>
+        <v>1516.5</v>
       </c>
       <c r="F26">
-        <v>3348.096</v>
+        <v>3487.6</v>
       </c>
       <c r="G26">
         <v>878.3</v>
@@ -3425,28 +3425,28 @@
         <v>839.6</v>
       </c>
       <c r="M26">
-        <v>181.8016128</v>
+        <v>189.37668</v>
       </c>
       <c r="N26">
-        <v>657.7983872</v>
+        <v>650.2233200000001</v>
       </c>
       <c r="O26">
-        <v>164.4495968</v>
+        <v>162.55583</v>
       </c>
       <c r="P26">
-        <v>493.3487904</v>
+        <v>487.66749</v>
       </c>
       <c r="Q26">
-        <v>665.1487903999999</v>
+        <v>659.46749</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08965875545354324</v>
+        <v>0.09012533795836816</v>
       </c>
       <c r="T26">
-        <v>0.8790899813354147</v>
+        <v>0.8884420024134509</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.618220856619375</v>
+        <v>4.433492022354601</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07777525346877612</v>
+        <v>0.07763585279285939</v>
       </c>
       <c r="C27">
-        <v>11185.81203125811</v>
+        <v>11106.71313345584</v>
       </c>
       <c r="D27">
-        <v>13795.11203125811</v>
+        <v>13855.51713345584</v>
       </c>
       <c r="E27">
-        <v>1516.5</v>
+        <v>1656.004</v>
       </c>
       <c r="F27">
-        <v>3487.6</v>
+        <v>3627.104</v>
       </c>
       <c r="G27">
         <v>878.3</v>
@@ -3507,28 +3507,28 @@
         <v>839.6</v>
       </c>
       <c r="M27">
-        <v>189.37668</v>
+        <v>196.9517472</v>
       </c>
       <c r="N27">
-        <v>650.2233200000001</v>
+        <v>642.6482528</v>
       </c>
       <c r="O27">
-        <v>162.55583</v>
+        <v>160.6620632</v>
       </c>
       <c r="P27">
-        <v>487.66749</v>
+        <v>481.9861896</v>
       </c>
       <c r="Q27">
-        <v>659.46749</v>
+        <v>653.7861895999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09012533795836816</v>
+        <v>0.09060453080116135</v>
       </c>
       <c r="T27">
-        <v>0.8884420024134509</v>
+        <v>0.8980467808179208</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.433492022354601</v>
+        <v>4.262973098417885</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07763585279285939</v>
+        <v>0.07769895211694267</v>
       </c>
       <c r="C28">
-        <v>11106.71313345584</v>
+        <v>10939.80153201676</v>
       </c>
       <c r="D28">
-        <v>13855.51713345584</v>
+        <v>13828.10953201676</v>
       </c>
       <c r="E28">
-        <v>1656.004</v>
+        <v>1795.508</v>
       </c>
       <c r="F28">
-        <v>3627.104</v>
+        <v>3766.608</v>
       </c>
       <c r="G28">
         <v>878.3</v>
@@ -3589,45 +3589,45 @@
         <v>839.6</v>
       </c>
       <c r="M28">
-        <v>196.9517472</v>
+        <v>208.2934224</v>
       </c>
       <c r="N28">
-        <v>642.6482528</v>
+        <v>631.3065776</v>
       </c>
       <c r="O28">
-        <v>160.6620632</v>
+        <v>157.8266444</v>
       </c>
       <c r="P28">
-        <v>481.9861896</v>
+        <v>473.4799332</v>
       </c>
       <c r="Q28">
-        <v>653.7861895999999</v>
+        <v>645.2799332</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09060453080116135</v>
+        <v>0.09109685221498995</v>
       </c>
       <c r="T28">
-        <v>0.8980467808179208</v>
+        <v>0.9079147038362116</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.262973098417885</v>
+        <v>4.030852200352534</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07769895211694267</v>
+        <v>0.07756705144102592</v>
       </c>
       <c r="C29">
-        <v>10939.80153201676</v>
+        <v>10857.71353102157</v>
       </c>
       <c r="D29">
-        <v>13828.10953201676</v>
+        <v>13885.52553102157</v>
       </c>
       <c r="E29">
-        <v>1795.508</v>
+        <v>1935.012</v>
       </c>
       <c r="F29">
-        <v>3766.608</v>
+        <v>3906.112</v>
       </c>
       <c r="G29">
         <v>878.3</v>
@@ -3671,28 +3671,28 @@
         <v>839.6</v>
       </c>
       <c r="M29">
-        <v>208.2934224</v>
+        <v>216.0079936</v>
       </c>
       <c r="N29">
-        <v>631.3065776</v>
+        <v>623.5920063999999</v>
       </c>
       <c r="O29">
-        <v>157.8266444</v>
+        <v>155.8980016</v>
       </c>
       <c r="P29">
-        <v>473.4799332</v>
+        <v>467.6940048</v>
       </c>
       <c r="Q29">
-        <v>645.2799332</v>
+        <v>639.4940047999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09109685221498995</v>
+        <v>0.09160284922364711</v>
       </c>
       <c r="T29">
-        <v>0.9079147038362116</v>
+        <v>0.9180567358272327</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.030852200352534</v>
+        <v>3.886893193197087</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07756705144102592</v>
+        <v>0.07743515076510918</v>
       </c>
       <c r="C30">
-        <v>10857.71353102157</v>
+        <v>10776.10431447305</v>
       </c>
       <c r="D30">
-        <v>13885.52553102157</v>
+        <v>13943.42031447305</v>
       </c>
       <c r="E30">
-        <v>1935.012</v>
+        <v>2074.516000000001</v>
       </c>
       <c r="F30">
-        <v>3906.112</v>
+        <v>4045.616</v>
       </c>
       <c r="G30">
         <v>878.3</v>
@@ -3753,28 +3753,28 @@
         <v>839.6</v>
       </c>
       <c r="M30">
-        <v>216.0079936</v>
+        <v>223.7225648</v>
       </c>
       <c r="N30">
-        <v>623.5920063999999</v>
+        <v>615.8774352</v>
       </c>
       <c r="O30">
-        <v>155.8980016</v>
+        <v>153.9693588</v>
       </c>
       <c r="P30">
-        <v>467.6940048</v>
+        <v>461.9080764</v>
       </c>
       <c r="Q30">
-        <v>639.4940047999999</v>
+        <v>633.7080764</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09160284922364711</v>
+        <v>0.09212309966916786</v>
       </c>
       <c r="T30">
-        <v>0.9180567358272327</v>
+        <v>0.9284844588602543</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.886893193197087</v>
+        <v>3.75286239343167</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07743515076510918</v>
+        <v>0.07730325008919244</v>
       </c>
       <c r="C31">
-        <v>10776.10431447305</v>
+        <v>10694.97989622615</v>
       </c>
       <c r="D31">
-        <v>13943.42031447305</v>
+        <v>14001.79989622615</v>
       </c>
       <c r="E31">
-        <v>2074.516</v>
+        <v>2214.02</v>
       </c>
       <c r="F31">
-        <v>4045.616</v>
+        <v>4185.12</v>
       </c>
       <c r="G31">
         <v>878.3</v>
@@ -3835,28 +3835,28 @@
         <v>839.6</v>
       </c>
       <c r="M31">
-        <v>223.7225648</v>
+        <v>231.437136</v>
       </c>
       <c r="N31">
-        <v>615.8774352</v>
+        <v>608.162864</v>
       </c>
       <c r="O31">
-        <v>153.9693588</v>
+        <v>152.040716</v>
       </c>
       <c r="P31">
-        <v>461.9080764</v>
+        <v>456.122148</v>
       </c>
       <c r="Q31">
-        <v>633.7080764</v>
+        <v>627.922148</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09212309966916786</v>
+        <v>0.09265821441313206</v>
       </c>
       <c r="T31">
-        <v>0.9284844588602543</v>
+        <v>0.9392101168370767</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.752862393431671</v>
+        <v>3.627766980317281</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07730325008919244</v>
+        <v>0.07717134941327571</v>
       </c>
       <c r="C32">
-        <v>10694.97989622615</v>
+        <v>10614.34639127669</v>
       </c>
       <c r="D32">
-        <v>14001.79989622615</v>
+        <v>14060.67039127669</v>
       </c>
       <c r="E32">
-        <v>2214.02</v>
+        <v>2353.524</v>
       </c>
       <c r="F32">
-        <v>4185.12</v>
+        <v>4324.624</v>
       </c>
       <c r="G32">
         <v>878.3</v>
@@ -3917,28 +3917,28 @@
         <v>839.6</v>
       </c>
       <c r="M32">
-        <v>231.437136</v>
+        <v>239.1517072</v>
       </c>
       <c r="N32">
-        <v>608.162864</v>
+        <v>600.4482928</v>
       </c>
       <c r="O32">
-        <v>152.040716</v>
+        <v>150.1120732</v>
       </c>
       <c r="P32">
-        <v>456.122148</v>
+        <v>450.3362196</v>
       </c>
       <c r="Q32">
-        <v>627.922148</v>
+        <v>622.1362196</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09265821441313206</v>
+        <v>0.09320883972938508</v>
       </c>
       <c r="T32">
-        <v>0.9392101168370767</v>
+        <v>0.9502466634509084</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.627766980317281</v>
+        <v>3.510742239016724</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07717134941327571</v>
+        <v>0.07703944873735896</v>
       </c>
       <c r="C33">
-        <v>10614.34639127669</v>
+        <v>10534.21001789662</v>
       </c>
       <c r="D33">
-        <v>14060.67039127669</v>
+        <v>14120.03801789662</v>
       </c>
       <c r="E33">
-        <v>2353.524</v>
+        <v>2493.028</v>
       </c>
       <c r="F33">
-        <v>4324.624</v>
+        <v>4464.128</v>
       </c>
       <c r="G33">
         <v>878.3</v>
@@ -3999,28 +3999,28 @@
         <v>839.6</v>
       </c>
       <c r="M33">
-        <v>239.1517072</v>
+        <v>246.8662784</v>
       </c>
       <c r="N33">
-        <v>600.4482928</v>
+        <v>592.7337216000001</v>
       </c>
       <c r="O33">
-        <v>150.1120732</v>
+        <v>148.1834304</v>
       </c>
       <c r="P33">
-        <v>450.3362196</v>
+        <v>444.5502912000001</v>
       </c>
       <c r="Q33">
-        <v>622.1362196</v>
+        <v>616.3502912</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09320883972938508</v>
+        <v>0.09377565990788084</v>
       </c>
       <c r="T33">
-        <v>0.9502466634509084</v>
+        <v>0.9616078143769117</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.510742239016724</v>
+        <v>3.401031544047452</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07703944873735896</v>
+        <v>0.07690754806144223</v>
       </c>
       <c r="C34">
-        <v>10534.21001789662</v>
+        <v>10454.57709982348</v>
       </c>
       <c r="D34">
-        <v>14120.03801789662</v>
+        <v>14179.90909982348</v>
       </c>
       <c r="E34">
-        <v>2493.028</v>
+        <v>2632.532000000001</v>
       </c>
       <c r="F34">
-        <v>4464.128</v>
+        <v>4603.632000000001</v>
       </c>
       <c r="G34">
         <v>878.3</v>
@@ -4081,28 +4081,28 @@
         <v>839.6</v>
       </c>
       <c r="M34">
-        <v>246.8662784</v>
+        <v>254.5808496000001</v>
       </c>
       <c r="N34">
-        <v>592.7337216000001</v>
+        <v>585.0191503999999</v>
       </c>
       <c r="O34">
-        <v>148.1834304</v>
+        <v>146.2547876</v>
       </c>
       <c r="P34">
-        <v>444.5502912000001</v>
+        <v>438.7643628</v>
       </c>
       <c r="Q34">
-        <v>616.3502912</v>
+        <v>610.5643627999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09377565990788084</v>
+        <v>0.09435940009170483</v>
       </c>
       <c r="T34">
-        <v>0.9616078143769117</v>
+        <v>0.9733081041365269</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.401031544047452</v>
+        <v>3.297969982106619</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07690754806144223</v>
+        <v>0.0767756473855255</v>
       </c>
       <c r="C35">
-        <v>10454.57709982348</v>
+        <v>10375.45406850595</v>
       </c>
       <c r="D35">
-        <v>14179.90909982348</v>
+        <v>14240.29006850595</v>
       </c>
       <c r="E35">
-        <v>2632.532000000001</v>
+        <v>2772.036000000001</v>
       </c>
       <c r="F35">
-        <v>4603.632000000001</v>
+        <v>4743.136</v>
       </c>
       <c r="G35">
         <v>878.3</v>
@@ -4163,28 +4163,28 @@
         <v>839.6</v>
       </c>
       <c r="M35">
-        <v>254.5808496000001</v>
+        <v>262.2954208</v>
       </c>
       <c r="N35">
-        <v>585.0191503999999</v>
+        <v>577.3045792</v>
       </c>
       <c r="O35">
-        <v>146.2547876</v>
+        <v>144.3261448</v>
       </c>
       <c r="P35">
-        <v>438.7643628</v>
+        <v>432.9784344</v>
       </c>
       <c r="Q35">
-        <v>610.5643627999999</v>
+        <v>604.7784343999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09435940009170483</v>
+        <v>0.09496082937200834</v>
       </c>
       <c r="T35">
-        <v>0.9733081041365269</v>
+        <v>0.985362948131282</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.297969982106619</v>
+        <v>3.200970864985836</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0767756473855255</v>
+        <v>0.07664374670960876</v>
       </c>
       <c r="C36">
-        <v>10375.45406850595</v>
+        <v>10296.84746540687</v>
       </c>
       <c r="D36">
-        <v>14240.29006850595</v>
+        <v>14301.18746540687</v>
       </c>
       <c r="E36">
-        <v>2772.036000000001</v>
+        <v>2911.54</v>
       </c>
       <c r="F36">
-        <v>4743.136</v>
+        <v>4882.64</v>
       </c>
       <c r="G36">
         <v>878.3</v>
@@ -4245,28 +4245,28 @@
         <v>839.6</v>
       </c>
       <c r="M36">
-        <v>262.2954208</v>
+        <v>270.009992</v>
       </c>
       <c r="N36">
-        <v>577.3045792</v>
+        <v>569.590008</v>
       </c>
       <c r="O36">
-        <v>144.3261448</v>
+        <v>142.397502</v>
       </c>
       <c r="P36">
-        <v>432.9784344</v>
+        <v>427.192506</v>
       </c>
       <c r="Q36">
-        <v>604.7784343999999</v>
+        <v>598.9925059999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09496082937200834</v>
+        <v>0.09558076416862887</v>
       </c>
       <c r="T36">
-        <v>0.985362948131282</v>
+        <v>0.9977887104027988</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.200970864985836</v>
+        <v>3.10951455455767</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07664374670960876</v>
+        <v>0.07651184603369202</v>
       </c>
       <c r="C37">
-        <v>10296.84746540687</v>
+        <v>10218.7639443657</v>
       </c>
       <c r="D37">
-        <v>14301.18746540687</v>
+        <v>14362.6079443657</v>
       </c>
       <c r="E37">
-        <v>2911.54</v>
+        <v>3051.044</v>
       </c>
       <c r="F37">
-        <v>4882.64</v>
+        <v>5022.144</v>
       </c>
       <c r="G37">
         <v>878.3</v>
@@ -4327,28 +4327,28 @@
         <v>839.6</v>
       </c>
       <c r="M37">
-        <v>270.009992</v>
+        <v>277.7245632</v>
       </c>
       <c r="N37">
-        <v>569.590008</v>
+        <v>561.8754368</v>
       </c>
       <c r="O37">
-        <v>142.397502</v>
+        <v>140.4688592</v>
       </c>
       <c r="P37">
-        <v>427.192506</v>
+        <v>421.4065776</v>
       </c>
       <c r="Q37">
-        <v>598.9925059999999</v>
+        <v>593.2065775999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09558076416862887</v>
+        <v>0.09622007192764379</v>
       </c>
       <c r="T37">
-        <v>0.9977887104027988</v>
+        <v>1.0106027777453</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.10951455455767</v>
+        <v>3.023139150264401</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07651184603369202</v>
+        <v>0.07707369535777528</v>
       </c>
       <c r="C38">
-        <v>10218.7639443657</v>
+        <v>9821.227707583403</v>
       </c>
       <c r="D38">
-        <v>14362.6079443657</v>
+        <v>14104.5757075834</v>
       </c>
       <c r="E38">
-        <v>3051.043999999999</v>
+        <v>3190.548</v>
       </c>
       <c r="F38">
-        <v>5022.143999999999</v>
+        <v>5161.648</v>
       </c>
       <c r="G38">
         <v>878.3</v>
@@ -4409,45 +4409,45 @@
         <v>839.6</v>
       </c>
       <c r="M38">
-        <v>277.7245632</v>
+        <v>298.3432544</v>
       </c>
       <c r="N38">
-        <v>561.8754368</v>
+        <v>541.2567455999999</v>
       </c>
       <c r="O38">
-        <v>140.4688592</v>
+        <v>135.3141864</v>
       </c>
       <c r="P38">
-        <v>421.4065776</v>
+        <v>405.9425591999999</v>
       </c>
       <c r="Q38">
-        <v>593.2065775999999</v>
+        <v>577.7425592</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09622007192764379</v>
+        <v>0.09687967517107188</v>
       </c>
       <c r="T38">
-        <v>1.0106027777453</v>
+        <v>1.023823640876453</v>
       </c>
       <c r="U38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.023139150264401</v>
+        <v>2.814208089566244</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07707369535777528</v>
+        <v>0.07696054468185856</v>
       </c>
       <c r="C39">
-        <v>9821.227707583403</v>
+        <v>9732.940471960464</v>
       </c>
       <c r="D39">
-        <v>14104.5757075834</v>
+        <v>14155.79247196047</v>
       </c>
       <c r="E39">
-        <v>3190.548</v>
+        <v>3330.052</v>
       </c>
       <c r="F39">
-        <v>5161.648</v>
+        <v>5301.152</v>
       </c>
       <c r="G39">
         <v>878.3</v>
@@ -4491,28 +4491,28 @@
         <v>839.6</v>
       </c>
       <c r="M39">
-        <v>298.3432544</v>
+        <v>306.4065856</v>
       </c>
       <c r="N39">
-        <v>541.2567455999999</v>
+        <v>533.1934143999999</v>
       </c>
       <c r="O39">
-        <v>135.3141864</v>
+        <v>133.2983536</v>
       </c>
       <c r="P39">
-        <v>405.9425591999999</v>
+        <v>399.8950608</v>
       </c>
       <c r="Q39">
-        <v>577.7425592</v>
+        <v>571.6950608</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09687967517107188</v>
+        <v>0.09756055593848154</v>
       </c>
       <c r="T39">
-        <v>1.023823640876453</v>
+        <v>1.037470983463449</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.814208089566244</v>
+        <v>2.74014998194608</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07696054468185856</v>
+        <v>0.07684739400594183</v>
       </c>
       <c r="C40">
-        <v>9732.940471960464</v>
+        <v>9645.026550214141</v>
       </c>
       <c r="D40">
-        <v>14155.79247196047</v>
+        <v>14207.38255021414</v>
       </c>
       <c r="E40">
-        <v>3330.052</v>
+        <v>3469.556</v>
       </c>
       <c r="F40">
-        <v>5301.152</v>
+        <v>5440.656</v>
       </c>
       <c r="G40">
         <v>878.3</v>
@@ -4573,28 +4573,28 @@
         <v>839.6</v>
       </c>
       <c r="M40">
-        <v>306.4065856</v>
+        <v>314.4699168</v>
       </c>
       <c r="N40">
-        <v>533.1934143999999</v>
+        <v>525.1300831999999</v>
       </c>
       <c r="O40">
-        <v>133.2983536</v>
+        <v>131.2825208</v>
       </c>
       <c r="P40">
-        <v>399.8950608</v>
+        <v>393.8475624</v>
       </c>
       <c r="Q40">
-        <v>571.6950608</v>
+        <v>565.6475624</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09756055593848154</v>
+        <v>0.0982637606654784</v>
       </c>
       <c r="T40">
-        <v>1.037470983463449</v>
+        <v>1.051565779905757</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.74014998194608</v>
+        <v>2.669889725998744</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07684739400594183</v>
+        <v>0.07673424333002507</v>
       </c>
       <c r="C41">
-        <v>9645.026550214141</v>
+        <v>9557.490038845241</v>
       </c>
       <c r="D41">
-        <v>14207.38255021414</v>
+        <v>14259.35003884524</v>
       </c>
       <c r="E41">
-        <v>3469.556</v>
+        <v>3609.06</v>
       </c>
       <c r="F41">
-        <v>5440.656</v>
+        <v>5580.16</v>
       </c>
       <c r="G41">
         <v>878.3</v>
@@ -4655,28 +4655,28 @@
         <v>839.6</v>
       </c>
       <c r="M41">
-        <v>314.4699168</v>
+        <v>322.533248</v>
       </c>
       <c r="N41">
-        <v>525.1300831999999</v>
+        <v>517.066752</v>
       </c>
       <c r="O41">
-        <v>131.2825208</v>
+        <v>129.266688</v>
       </c>
       <c r="P41">
-        <v>393.8475624</v>
+        <v>387.800064</v>
       </c>
       <c r="Q41">
-        <v>565.6475624</v>
+        <v>559.600064</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0982637606654784</v>
+        <v>0.09899040555004179</v>
       </c>
       <c r="T41">
-        <v>1.051565779905757</v>
+        <v>1.066130402896141</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.669889725998744</v>
+        <v>2.603142482848776</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07673424333002507</v>
+        <v>0.07662109265410835</v>
       </c>
       <c r="C42">
-        <v>9557.490038845241</v>
+        <v>9470.335094510965</v>
       </c>
       <c r="D42">
-        <v>14259.35003884524</v>
+        <v>14311.69909451097</v>
       </c>
       <c r="E42">
-        <v>3609.06</v>
+        <v>3748.564000000001</v>
       </c>
       <c r="F42">
-        <v>5580.16</v>
+        <v>5719.664000000001</v>
       </c>
       <c r="G42">
         <v>878.3</v>
@@ -4737,28 +4737,28 @@
         <v>839.6</v>
       </c>
       <c r="M42">
-        <v>322.533248</v>
+        <v>330.5965792000001</v>
       </c>
       <c r="N42">
-        <v>517.066752</v>
+        <v>509.0034208</v>
       </c>
       <c r="O42">
-        <v>129.266688</v>
+        <v>127.2508552</v>
       </c>
       <c r="P42">
-        <v>387.800064</v>
+        <v>381.7525656</v>
       </c>
       <c r="Q42">
-        <v>559.600064</v>
+        <v>553.5525656</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09899040555004179</v>
+        <v>0.09974168246459042</v>
       </c>
       <c r="T42">
-        <v>1.066130402896141</v>
+        <v>1.081188741920098</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.603142482848776</v>
+        <v>2.539651202779293</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07662109265410835</v>
+        <v>0.07761044197819161</v>
       </c>
       <c r="C43">
-        <v>9470.335094510965</v>
+        <v>8885.717196522855</v>
       </c>
       <c r="D43">
-        <v>14311.69909451097</v>
+        <v>13866.58519652286</v>
       </c>
       <c r="E43">
-        <v>3748.564000000001</v>
+        <v>3888.068000000001</v>
       </c>
       <c r="F43">
-        <v>5719.664000000001</v>
+        <v>5859.168000000001</v>
       </c>
       <c r="G43">
         <v>878.3</v>
@@ -4819,45 +4819,45 @@
         <v>839.6</v>
       </c>
       <c r="M43">
-        <v>330.5965792000001</v>
+        <v>359.1669984</v>
       </c>
       <c r="N43">
-        <v>509.0034208</v>
+        <v>480.4330016</v>
       </c>
       <c r="O43">
-        <v>127.2508552</v>
+        <v>120.1082504</v>
       </c>
       <c r="P43">
-        <v>381.7525656</v>
+        <v>360.3247512</v>
       </c>
       <c r="Q43">
-        <v>553.5525656</v>
+        <v>532.1247512</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09974168246459042</v>
+        <v>0.1005188654796407</v>
       </c>
       <c r="T43">
-        <v>1.081188741920098</v>
+        <v>1.096766334013846</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.539651202779293</v>
+        <v>2.337631251591071</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07761044197819161</v>
+        <v>0.07752354130227487</v>
       </c>
       <c r="C44">
-        <v>8885.717196522855</v>
+        <v>8784.198099114688</v>
       </c>
       <c r="D44">
-        <v>13866.58519652286</v>
+        <v>13904.57009911469</v>
       </c>
       <c r="E44">
-        <v>3888.068</v>
+        <v>4027.572</v>
       </c>
       <c r="F44">
-        <v>5859.168</v>
+        <v>5998.672</v>
       </c>
       <c r="G44">
         <v>878.3</v>
@@ -4901,28 +4901,28 @@
         <v>839.6</v>
       </c>
       <c r="M44">
-        <v>359.1669984</v>
+        <v>367.7185936</v>
       </c>
       <c r="N44">
-        <v>480.4330016000001</v>
+        <v>471.8814064000001</v>
       </c>
       <c r="O44">
-        <v>120.1082504</v>
+        <v>117.9703516</v>
       </c>
       <c r="P44">
-        <v>360.3247512</v>
+        <v>353.9110548</v>
       </c>
       <c r="Q44">
-        <v>532.1247512</v>
+        <v>525.7110548000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1005188654796407</v>
+        <v>0.1013233180741664</v>
       </c>
       <c r="T44">
-        <v>1.096766334013846</v>
+        <v>1.112890508286323</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.337631251591071</v>
+        <v>2.283267734112209</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07752354130227487</v>
+        <v>0.07836064062635814</v>
       </c>
       <c r="C45">
-        <v>8784.198099114688</v>
+        <v>8287.222439843494</v>
       </c>
       <c r="D45">
-        <v>13904.57009911469</v>
+        <v>13547.09843984349</v>
       </c>
       <c r="E45">
-        <v>4027.572</v>
+        <v>4167.075999999999</v>
       </c>
       <c r="F45">
-        <v>5998.672</v>
+        <v>6138.175999999999</v>
       </c>
       <c r="G45">
         <v>878.3</v>
@@ -4983,45 +4983,45 @@
         <v>839.6</v>
       </c>
       <c r="M45">
-        <v>367.7185936</v>
+        <v>393.4570816</v>
       </c>
       <c r="N45">
-        <v>471.8814064000001</v>
+        <v>446.1429184</v>
       </c>
       <c r="O45">
-        <v>117.9703516</v>
+        <v>111.5357296</v>
       </c>
       <c r="P45">
-        <v>353.9110548</v>
+        <v>334.6071888</v>
       </c>
       <c r="Q45">
-        <v>525.7110548000001</v>
+        <v>506.4071888</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1013233180741664</v>
+        <v>0.1021565011184967</v>
       </c>
       <c r="T45">
-        <v>1.112890508286323</v>
+        <v>1.129590545925673</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.283267734112209</v>
+        <v>2.133904914319377</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07836064062635814</v>
+        <v>0.07829473995044141</v>
       </c>
       <c r="C46">
-        <v>8287.222439843494</v>
+        <v>8175.192515501825</v>
       </c>
       <c r="D46">
-        <v>13547.09843984349</v>
+        <v>13574.57251550183</v>
       </c>
       <c r="E46">
-        <v>4167.075999999999</v>
+        <v>4306.58</v>
       </c>
       <c r="F46">
-        <v>6138.175999999999</v>
+        <v>6277.68</v>
       </c>
       <c r="G46">
         <v>878.3</v>
@@ -5065,28 +5065,28 @@
         <v>839.6</v>
       </c>
       <c r="M46">
-        <v>393.4570816</v>
+        <v>402.3992880000001</v>
       </c>
       <c r="N46">
-        <v>446.1429184</v>
+        <v>437.200712</v>
       </c>
       <c r="O46">
-        <v>111.5357296</v>
+        <v>109.300178</v>
       </c>
       <c r="P46">
-        <v>334.6071888</v>
+        <v>327.900534</v>
       </c>
       <c r="Q46">
-        <v>506.4071888</v>
+        <v>499.7005339999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1021565011184967</v>
+        <v>0.1030199817280753</v>
       </c>
       <c r="T46">
-        <v>1.129590545925673</v>
+        <v>1.146897857661</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.133904914319377</v>
+        <v>2.086484805112279</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07829473995044141</v>
+        <v>0.07822883927452466</v>
       </c>
       <c r="C47">
-        <v>8175.192515501825</v>
+        <v>8063.274254740888</v>
       </c>
       <c r="D47">
-        <v>13574.57251550183</v>
+        <v>13602.15825474089</v>
       </c>
       <c r="E47">
-        <v>4306.58</v>
+        <v>4446.084000000001</v>
       </c>
       <c r="F47">
-        <v>6277.68</v>
+        <v>6417.184</v>
       </c>
       <c r="G47">
         <v>878.3</v>
@@ -5147,28 +5147,28 @@
         <v>839.6</v>
       </c>
       <c r="M47">
-        <v>402.3992880000001</v>
+        <v>411.3414944</v>
       </c>
       <c r="N47">
-        <v>437.200712</v>
+        <v>428.2585056</v>
       </c>
       <c r="O47">
-        <v>109.300178</v>
+        <v>107.0646264</v>
       </c>
       <c r="P47">
-        <v>327.900534</v>
+        <v>321.1938792</v>
       </c>
       <c r="Q47">
-        <v>499.7005339999999</v>
+        <v>492.9938791999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1030199817280753</v>
+        <v>0.1039154431009716</v>
       </c>
       <c r="T47">
-        <v>1.146897857661</v>
+        <v>1.16484618094208</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.086484805112279</v>
+        <v>2.041126439783751</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07822883927452466</v>
+        <v>0.08091243859860793</v>
       </c>
       <c r="C48">
-        <v>8063.274254740888</v>
+        <v>6884.174483117566</v>
       </c>
       <c r="D48">
-        <v>13602.15825474089</v>
+        <v>12562.56248311757</v>
       </c>
       <c r="E48">
-        <v>4446.084000000001</v>
+        <v>4585.588</v>
       </c>
       <c r="F48">
-        <v>6417.184</v>
+        <v>6556.688</v>
       </c>
       <c r="G48">
         <v>878.3</v>
@@ -5229,45 +5229,45 @@
         <v>839.6</v>
       </c>
       <c r="M48">
-        <v>411.3414944</v>
+        <v>471.4258672</v>
       </c>
       <c r="N48">
-        <v>428.2585056</v>
+        <v>368.1741328</v>
       </c>
       <c r="O48">
-        <v>107.0646264</v>
+        <v>92.0435332</v>
       </c>
       <c r="P48">
-        <v>321.1938792</v>
+        <v>276.1305996</v>
       </c>
       <c r="Q48">
-        <v>492.9938791999999</v>
+        <v>447.9305995999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1039154431009716</v>
+        <v>0.1048446954690715</v>
       </c>
       <c r="T48">
-        <v>1.16484618094208</v>
+        <v>1.183471799441314</v>
       </c>
       <c r="U48">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.041126439783751</v>
+        <v>1.780979913102231</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08091243859860793</v>
+        <v>0.08230903792269119</v>
       </c>
       <c r="C49">
-        <v>6884.174483117566</v>
+        <v>6264.108209473779</v>
       </c>
       <c r="D49">
-        <v>12562.56248311757</v>
+        <v>12082.00020947378</v>
       </c>
       <c r="E49">
-        <v>4585.588</v>
+        <v>4725.092000000001</v>
       </c>
       <c r="F49">
-        <v>6556.688</v>
+        <v>6696.192</v>
       </c>
       <c r="G49">
         <v>878.3</v>
@@ -5311,45 +5311,45 @@
         <v>839.6</v>
       </c>
       <c r="M49">
-        <v>471.4258672</v>
+        <v>507.5713536000001</v>
       </c>
       <c r="N49">
-        <v>368.1741328</v>
+        <v>332.0286464</v>
       </c>
       <c r="O49">
-        <v>92.0435332</v>
+        <v>83.00716159999999</v>
       </c>
       <c r="P49">
-        <v>276.1305996</v>
+        <v>249.0214848</v>
       </c>
       <c r="Q49">
-        <v>447.9305995999999</v>
+        <v>420.8214847999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1048446954690715</v>
+        <v>0.1058096883128677</v>
       </c>
       <c r="T49">
-        <v>1.183471799441314</v>
+        <v>1.202813787882826</v>
       </c>
       <c r="U49">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.780979913102231</v>
+        <v>1.654151665662481</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08230903792269119</v>
+        <v>0.08233088724677445</v>
       </c>
       <c r="C50">
-        <v>6264.108209473779</v>
+        <v>6117.377898862498</v>
       </c>
       <c r="D50">
-        <v>12082.00020947378</v>
+        <v>12074.7738988625</v>
       </c>
       <c r="E50">
-        <v>4725.092000000001</v>
+        <v>4864.596</v>
       </c>
       <c r="F50">
-        <v>6696.192</v>
+        <v>6835.696</v>
       </c>
       <c r="G50">
         <v>878.3</v>
@@ -5393,28 +5393,28 @@
         <v>839.6</v>
       </c>
       <c r="M50">
-        <v>507.5713536000001</v>
+        <v>518.1457568000001</v>
       </c>
       <c r="N50">
-        <v>332.0286464</v>
+        <v>321.4542432</v>
       </c>
       <c r="O50">
-        <v>83.00716159999999</v>
+        <v>80.36356079999999</v>
       </c>
       <c r="P50">
-        <v>249.0214848</v>
+        <v>241.0906824</v>
       </c>
       <c r="Q50">
-        <v>420.8214847999999</v>
+        <v>412.8906823999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1058096883128677</v>
+        <v>0.1068125240132832</v>
       </c>
       <c r="T50">
-        <v>1.202813787882826</v>
+        <v>1.222914285674985</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.654151665662481</v>
+        <v>1.620393468404063</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08233088724677445</v>
+        <v>0.08235273657085772</v>
       </c>
       <c r="C51">
-        <v>6117.377898862498</v>
+        <v>5970.656227276214</v>
       </c>
       <c r="D51">
-        <v>12074.7738988625</v>
+        <v>12067.55622727621</v>
       </c>
       <c r="E51">
-        <v>4864.596</v>
+        <v>5004.1</v>
       </c>
       <c r="F51">
-        <v>6835.696</v>
+        <v>6975.2</v>
       </c>
       <c r="G51">
         <v>878.3</v>
@@ -5475,28 +5475,28 @@
         <v>839.6</v>
       </c>
       <c r="M51">
-        <v>518.1457568000001</v>
+        <v>528.7201600000001</v>
       </c>
       <c r="N51">
-        <v>321.4542432</v>
+        <v>310.8798399999999</v>
       </c>
       <c r="O51">
-        <v>80.36356079999999</v>
+        <v>77.71995999999999</v>
       </c>
       <c r="P51">
-        <v>241.0906824</v>
+        <v>233.15988</v>
       </c>
       <c r="Q51">
-        <v>412.8906823999999</v>
+        <v>404.9598799999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1068125240132832</v>
+        <v>0.1078554731417154</v>
       </c>
       <c r="T51">
-        <v>1.222914285674985</v>
+        <v>1.243818803378831</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.620393468404063</v>
+        <v>1.587985599035981</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08235273657085772</v>
+        <v>0.08237458589494098</v>
       </c>
       <c r="C52">
-        <v>5970.656227276214</v>
+        <v>5823.943179232305</v>
       </c>
       <c r="D52">
-        <v>12067.55622727621</v>
+        <v>12060.34717923231</v>
       </c>
       <c r="E52">
-        <v>5004.1</v>
+        <v>5143.603999999999</v>
       </c>
       <c r="F52">
-        <v>6975.2</v>
+        <v>7114.704</v>
       </c>
       <c r="G52">
         <v>878.3</v>
@@ -5557,28 +5557,28 @@
         <v>839.6</v>
       </c>
       <c r="M52">
-        <v>528.7201600000001</v>
+        <v>539.2945632</v>
       </c>
       <c r="N52">
-        <v>310.8798399999999</v>
+        <v>300.3054368000001</v>
       </c>
       <c r="O52">
-        <v>77.71995999999999</v>
+        <v>75.07635920000001</v>
       </c>
       <c r="P52">
-        <v>233.15988</v>
+        <v>225.2290776</v>
       </c>
       <c r="Q52">
-        <v>404.9598799999999</v>
+        <v>397.0290776</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1078554731417154</v>
+        <v>0.1089409916223285</v>
       </c>
       <c r="T52">
-        <v>1.243818803378831</v>
+        <v>1.265576566703242</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.587985599035981</v>
+        <v>1.556848626505865</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08237458589494098</v>
+        <v>0.08239643521902426</v>
       </c>
       <c r="C53">
-        <v>5823.943179232305</v>
+        <v>5677.238739285113</v>
       </c>
       <c r="D53">
-        <v>12060.34717923231</v>
+        <v>12053.14673928511</v>
       </c>
       <c r="E53">
-        <v>5143.603999999999</v>
+        <v>5283.108</v>
       </c>
       <c r="F53">
-        <v>7114.704</v>
+        <v>7254.208</v>
       </c>
       <c r="G53">
         <v>878.3</v>
@@ -5639,28 +5639,28 @@
         <v>839.6</v>
       </c>
       <c r="M53">
-        <v>539.2945632</v>
+        <v>549.8689664</v>
       </c>
       <c r="N53">
-        <v>300.3054368000001</v>
+        <v>289.7310336</v>
       </c>
       <c r="O53">
-        <v>75.07635920000001</v>
+        <v>72.43275840000001</v>
       </c>
       <c r="P53">
-        <v>225.2290776</v>
+        <v>217.2982752</v>
       </c>
       <c r="Q53">
-        <v>397.0290776</v>
+        <v>389.0982752</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1089409916223285</v>
+        <v>0.1100717400396339</v>
       </c>
       <c r="T53">
-        <v>1.265576566703242</v>
+        <v>1.288240903499504</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.556848626505865</v>
+        <v>1.52690922984229</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08239643521902426</v>
+        <v>0.08806278454310751</v>
       </c>
       <c r="C54">
-        <v>5677.238739285113</v>
+        <v>3921.718648117195</v>
       </c>
       <c r="D54">
-        <v>12053.14673928511</v>
+        <v>10437.1306481172</v>
       </c>
       <c r="E54">
-        <v>5283.108</v>
+        <v>5422.612000000001</v>
       </c>
       <c r="F54">
-        <v>7254.208</v>
+        <v>7393.712</v>
       </c>
       <c r="G54">
         <v>878.3</v>
@@ -5721,45 +5721,45 @@
         <v>839.6</v>
       </c>
       <c r="M54">
-        <v>549.8689664</v>
+        <v>665.43408</v>
       </c>
       <c r="N54">
-        <v>289.7310336</v>
+        <v>174.16592</v>
       </c>
       <c r="O54">
-        <v>72.43275840000001</v>
+        <v>43.54148000000001</v>
       </c>
       <c r="P54">
-        <v>217.2982752</v>
+        <v>130.62444</v>
       </c>
       <c r="Q54">
-        <v>389.0982752</v>
+        <v>302.42444</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1100717400396339</v>
+        <v>0.111250605410867</v>
       </c>
       <c r="T54">
-        <v>1.288240903499504</v>
+        <v>1.311869680159436</v>
       </c>
       <c r="U54">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.52690922984229</v>
+        <v>1.261732792525444</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08806278454310751</v>
+        <v>0.1010274472248066</v>
       </c>
       <c r="C55">
-        <v>3921.718648117195</v>
+        <v>1332.094553540675</v>
       </c>
       <c r="D55">
-        <v>10437.1306481172</v>
+        <v>7987.010553540676</v>
       </c>
       <c r="E55">
-        <v>5422.612000000001</v>
+        <v>5562.116</v>
       </c>
       <c r="F55">
-        <v>7393.712</v>
+        <v>7533.216</v>
       </c>
       <c r="G55">
         <v>878.3</v>
@@ -5803,45 +5803,45 @@
         <v>839.6</v>
       </c>
       <c r="M55">
-        <v>665.43408</v>
+        <v>893.4394176000001</v>
       </c>
       <c r="N55">
-        <v>174.16592</v>
+        <v>-53.83941760000005</v>
       </c>
       <c r="O55">
-        <v>43.54148000000001</v>
+        <v>-13.45985440000001</v>
       </c>
       <c r="P55">
-        <v>130.62444</v>
+        <v>-40.37956320000004</v>
       </c>
       <c r="Q55">
-        <v>302.42444</v>
+        <v>131.4204367999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.111250605410867</v>
+        <v>0.1131078495123316</v>
       </c>
       <c r="T55">
-        <v>1.311869680159436</v>
+        <v>1.349095649423912</v>
       </c>
       <c r="U55">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V55">
-        <v>0.25</v>
+        <v>0.2349347878156568</v>
       </c>
       <c r="W55">
-        <v>0.0675</v>
+        <v>0.09073673416506312</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.261732792525444</v>
+        <v>0.9397391512626272</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1010274472248066</v>
+        <v>0.1017554472248066</v>
       </c>
       <c r="C56">
-        <v>1332.094553540675</v>
+        <v>1088.67674404833</v>
       </c>
       <c r="D56">
-        <v>7987.010553540676</v>
+        <v>7883.09674404833</v>
       </c>
       <c r="E56">
-        <v>5562.116</v>
+        <v>5701.620000000001</v>
       </c>
       <c r="F56">
-        <v>7533.216</v>
+        <v>7672.72</v>
       </c>
       <c r="G56">
         <v>878.3</v>
@@ -5885,37 +5885,37 @@
         <v>839.6</v>
       </c>
       <c r="M56">
-        <v>893.4394176000001</v>
+        <v>909.9845920000001</v>
       </c>
       <c r="N56">
-        <v>-53.83941760000005</v>
+        <v>-70.38459200000011</v>
       </c>
       <c r="O56">
-        <v>-13.45985440000001</v>
+        <v>-17.59614800000003</v>
       </c>
       <c r="P56">
-        <v>-40.37956320000004</v>
+        <v>-52.78844400000008</v>
       </c>
       <c r="Q56">
-        <v>131.4204367999999</v>
+        <v>119.0115559999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1131078495123316</v>
+        <v>0.1146035795014945</v>
       </c>
       <c r="T56">
-        <v>1.349095649423912</v>
+        <v>1.379075552744444</v>
       </c>
       <c r="U56">
         <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.2349347878156568</v>
+        <v>0.2306632462190085</v>
       </c>
       <c r="W56">
-        <v>0.09073673416506312</v>
+        <v>0.0912433389984256</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9397391512626272</v>
+        <v>0.9226529848760339</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1017554472248066</v>
+        <v>0.1024834472248066</v>
       </c>
       <c r="C57">
-        <v>1088.67674404833</v>
+        <v>847.9281177836874</v>
       </c>
       <c r="D57">
-        <v>7883.09674404833</v>
+        <v>7781.852117783687</v>
       </c>
       <c r="E57">
-        <v>5701.620000000001</v>
+        <v>5841.124</v>
       </c>
       <c r="F57">
-        <v>7672.72</v>
+        <v>7812.224</v>
       </c>
       <c r="G57">
         <v>878.3</v>
@@ -5967,37 +5967,37 @@
         <v>839.6</v>
       </c>
       <c r="M57">
-        <v>909.9845920000001</v>
+        <v>926.5297664000001</v>
       </c>
       <c r="N57">
-        <v>-70.38459200000011</v>
+        <v>-86.92976640000006</v>
       </c>
       <c r="O57">
-        <v>-17.59614800000003</v>
+        <v>-21.73244160000002</v>
       </c>
       <c r="P57">
-        <v>-52.78844400000008</v>
+        <v>-65.19732480000005</v>
       </c>
       <c r="Q57">
-        <v>119.0115559999999</v>
+        <v>106.6026751999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1146035795014945</v>
+        <v>0.1161672972174376</v>
       </c>
       <c r="T57">
-        <v>1.379075552744444</v>
+        <v>1.410418178943181</v>
       </c>
       <c r="U57">
         <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.2306632462190085</v>
+        <v>0.2265442596793834</v>
       </c>
       <c r="W57">
-        <v>0.0912433389984256</v>
+        <v>0.09173185080202513</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9226529848760339</v>
+        <v>0.9061770387175334</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1024834472248066</v>
+        <v>0.1032114472248066</v>
       </c>
       <c r="C58">
-        <v>847.9281177836874</v>
+        <v>609.7471358298371</v>
       </c>
       <c r="D58">
-        <v>7781.852117783687</v>
+        <v>7683.175135829839</v>
       </c>
       <c r="E58">
-        <v>5841.124</v>
+        <v>5980.628000000001</v>
       </c>
       <c r="F58">
-        <v>7812.224</v>
+        <v>7951.728000000001</v>
       </c>
       <c r="G58">
         <v>878.3</v>
@@ -6049,37 +6049,37 @@
         <v>839.6</v>
       </c>
       <c r="M58">
-        <v>926.5297664000001</v>
+        <v>943.0749408000001</v>
       </c>
       <c r="N58">
-        <v>-86.92976640000006</v>
+        <v>-103.4749408000001</v>
       </c>
       <c r="O58">
-        <v>-21.73244160000002</v>
+        <v>-25.86873520000003</v>
       </c>
       <c r="P58">
-        <v>-65.19732480000005</v>
+        <v>-77.6062056000001</v>
       </c>
       <c r="Q58">
-        <v>106.6026751999999</v>
+        <v>94.19379439999986</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1161672972174376</v>
+        <v>0.1178037459899361</v>
       </c>
       <c r="T58">
-        <v>1.410418178943181</v>
+        <v>1.443218601709302</v>
       </c>
       <c r="U58">
         <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.2265442596793834</v>
+        <v>0.2225697989832538</v>
       </c>
       <c r="W58">
-        <v>0.09173185080202513</v>
+        <v>0.0922032218405861</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9061770387175334</v>
+        <v>0.8902791959330152</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1032114472248066</v>
+        <v>0.1039394472248066</v>
       </c>
       <c r="C59">
-        <v>609.7471358298371</v>
+        <v>374.0373449963508</v>
       </c>
       <c r="D59">
-        <v>7683.175135829839</v>
+        <v>7586.969344996352</v>
       </c>
       <c r="E59">
-        <v>5980.628000000001</v>
+        <v>6120.132000000001</v>
       </c>
       <c r="F59">
-        <v>7951.728000000001</v>
+        <v>8091.232000000001</v>
       </c>
       <c r="G59">
         <v>878.3</v>
@@ -6131,37 +6131,37 @@
         <v>839.6</v>
       </c>
       <c r="M59">
-        <v>943.0749408000001</v>
+        <v>959.6201152000002</v>
       </c>
       <c r="N59">
-        <v>-103.4749408000001</v>
+        <v>-120.0201152000002</v>
       </c>
       <c r="O59">
-        <v>-25.86873520000003</v>
+        <v>-30.00502880000005</v>
       </c>
       <c r="P59">
-        <v>-77.6062056000001</v>
+        <v>-90.01508640000014</v>
       </c>
       <c r="Q59">
-        <v>94.19379439999986</v>
+        <v>81.78491359999981</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1178037459899361</v>
+        <v>0.1195181208944584</v>
       </c>
       <c r="T59">
-        <v>1.443218601709302</v>
+        <v>1.477580949369047</v>
       </c>
       <c r="U59">
         <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.2225697989832538</v>
+        <v>0.2187323886559563</v>
       </c>
       <c r="W59">
-        <v>0.0922032218405861</v>
+        <v>0.0926583387054036</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8902791959330152</v>
+        <v>0.8749295546238252</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1039394472248066</v>
+        <v>0.1046674472248066</v>
       </c>
       <c r="C60">
-        <v>374.0373449963563</v>
+        <v>140.7070633493113</v>
       </c>
       <c r="D60">
-        <v>7586.969344996355</v>
+        <v>7493.143063349311</v>
       </c>
       <c r="E60">
-        <v>6120.132</v>
+        <v>6259.635999999999</v>
       </c>
       <c r="F60">
-        <v>8091.231999999999</v>
+        <v>8230.735999999999</v>
       </c>
       <c r="G60">
         <v>878.3</v>
@@ -6213,37 +6213,37 @@
         <v>839.6</v>
       </c>
       <c r="M60">
-        <v>959.6201152</v>
+        <v>976.1652895999999</v>
       </c>
       <c r="N60">
-        <v>-120.0201152</v>
+        <v>-136.5652895999999</v>
       </c>
       <c r="O60">
-        <v>-30.00502879999999</v>
+        <v>-34.14132239999998</v>
       </c>
       <c r="P60">
-        <v>-90.01508639999997</v>
+        <v>-102.4239671999999</v>
       </c>
       <c r="Q60">
-        <v>81.78491359999998</v>
+        <v>69.37603280000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1195181208944584</v>
+        <v>0.1213161238431037</v>
       </c>
       <c r="T60">
-        <v>1.477580949369046</v>
+        <v>1.513619509109755</v>
       </c>
       <c r="U60">
         <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.2187323886559563</v>
+        <v>0.215025060034669</v>
       </c>
       <c r="W60">
-        <v>0.09265833870540359</v>
+        <v>0.09309802787988826</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8749295546238254</v>
+        <v>0.8601002401386759</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1046674472248066</v>
+        <v>0.1053954472248066</v>
       </c>
       <c r="C61">
-        <v>140.7070633493113</v>
+        <v>-90.33091120986865</v>
       </c>
       <c r="D61">
-        <v>7493.143063349311</v>
+        <v>7401.609088790131</v>
       </c>
       <c r="E61">
-        <v>6259.635999999999</v>
+        <v>6399.139999999999</v>
       </c>
       <c r="F61">
-        <v>8230.735999999999</v>
+        <v>8370.24</v>
       </c>
       <c r="G61">
         <v>878.3</v>
@@ -6295,37 +6295,37 @@
         <v>839.6</v>
       </c>
       <c r="M61">
-        <v>976.1652895999999</v>
+        <v>992.7104640000001</v>
       </c>
       <c r="N61">
-        <v>-136.5652895999999</v>
+        <v>-153.1104640000001</v>
       </c>
       <c r="O61">
-        <v>-34.14132239999998</v>
+        <v>-38.27761600000002</v>
       </c>
       <c r="P61">
-        <v>-102.4239671999999</v>
+        <v>-114.8328480000001</v>
       </c>
       <c r="Q61">
-        <v>69.37603280000002</v>
+        <v>56.96715199999988</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1213161238431037</v>
+        <v>0.1232040269391813</v>
       </c>
       <c r="T61">
-        <v>1.513619509109755</v>
+        <v>1.551459996837498</v>
       </c>
       <c r="U61">
         <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.215025060034669</v>
+        <v>0.2114413090340911</v>
       </c>
       <c r="W61">
-        <v>0.09309802787988826</v>
+        <v>0.0935230607485568</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8601002401386759</v>
+        <v>0.8457652361363645</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1053954472248066</v>
+        <v>0.1061234472248066</v>
       </c>
       <c r="C62">
-        <v>-90.33091120986865</v>
+        <v>-319.1595712638355</v>
       </c>
       <c r="D62">
-        <v>7401.609088790131</v>
+        <v>7312.284428736163</v>
       </c>
       <c r="E62">
-        <v>6399.139999999999</v>
+        <v>6538.643999999998</v>
       </c>
       <c r="F62">
-        <v>8370.24</v>
+        <v>8509.743999999999</v>
       </c>
       <c r="G62">
         <v>878.3</v>
@@ -6377,37 +6377,37 @@
         <v>839.6</v>
       </c>
       <c r="M62">
-        <v>992.7104640000001</v>
+        <v>1009.2556384</v>
       </c>
       <c r="N62">
-        <v>-153.1104640000001</v>
+        <v>-169.6556383999999</v>
       </c>
       <c r="O62">
-        <v>-38.27761600000002</v>
+        <v>-42.41390959999998</v>
       </c>
       <c r="P62">
-        <v>-114.8328480000001</v>
+        <v>-127.2417287999999</v>
       </c>
       <c r="Q62">
-        <v>56.96715199999988</v>
+        <v>44.55827120000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1232040269391813</v>
+        <v>0.1251887455786475</v>
       </c>
       <c r="T62">
-        <v>1.551459996837498</v>
+        <v>1.591241022397435</v>
       </c>
       <c r="U62">
         <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.2114413090340911</v>
+        <v>0.2079750580663192</v>
       </c>
       <c r="W62">
-        <v>0.0935230607485568</v>
+        <v>0.09393415811333457</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8457652361363645</v>
+        <v>0.8319002322652767</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1061234472248066</v>
+        <v>0.1068514472248066</v>
       </c>
       <c r="C63">
-        <v>-319.1595712638355</v>
+        <v>-545.8579508584435</v>
       </c>
       <c r="D63">
-        <v>7312.284428736163</v>
+        <v>7225.090049141556</v>
       </c>
       <c r="E63">
-        <v>6538.643999999998</v>
+        <v>6678.147999999999</v>
       </c>
       <c r="F63">
-        <v>8509.743999999999</v>
+        <v>8649.248</v>
       </c>
       <c r="G63">
         <v>878.3</v>
@@ -6459,37 +6459,37 @@
         <v>839.6</v>
       </c>
       <c r="M63">
-        <v>1009.2556384</v>
+        <v>1025.8008128</v>
       </c>
       <c r="N63">
-        <v>-169.6556383999999</v>
+        <v>-186.2008128000001</v>
       </c>
       <c r="O63">
-        <v>-42.41390959999998</v>
+        <v>-46.55020320000003</v>
       </c>
       <c r="P63">
-        <v>-127.2417287999999</v>
+        <v>-139.6506096000001</v>
       </c>
       <c r="Q63">
-        <v>44.55827120000001</v>
+        <v>32.14939039999987</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1251887455786475</v>
+        <v>0.1272779230938751</v>
       </c>
       <c r="T63">
-        <v>1.591241022397435</v>
+        <v>1.633115786144735</v>
       </c>
       <c r="U63">
         <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.2079750580663192</v>
+        <v>0.2046206216458946</v>
       </c>
       <c r="W63">
-        <v>0.09393415811333457</v>
+        <v>0.09433199427279691</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8319002322652767</v>
+        <v>0.8184824865835785</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1068514472248066</v>
+        <v>0.1075794472248066</v>
       </c>
       <c r="C64">
-        <v>-545.8579508584435</v>
+        <v>-770.5013587368467</v>
       </c>
       <c r="D64">
-        <v>7225.090049141556</v>
+        <v>7139.950641263154</v>
       </c>
       <c r="E64">
-        <v>6678.147999999999</v>
+        <v>6817.652</v>
       </c>
       <c r="F64">
-        <v>8649.248</v>
+        <v>8788.752</v>
       </c>
       <c r="G64">
         <v>878.3</v>
@@ -6541,37 +6541,37 @@
         <v>839.6</v>
       </c>
       <c r="M64">
-        <v>1025.8008128</v>
+        <v>1042.3459872</v>
       </c>
       <c r="N64">
-        <v>-186.2008128000001</v>
+        <v>-202.7459872000001</v>
       </c>
       <c r="O64">
-        <v>-46.55020320000003</v>
+        <v>-50.68649680000001</v>
       </c>
       <c r="P64">
-        <v>-139.6506096000001</v>
+        <v>-152.0594904</v>
       </c>
       <c r="Q64">
-        <v>32.14939039999987</v>
+        <v>19.74050959999991</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1272779230938751</v>
+        <v>0.1294800291234393</v>
       </c>
       <c r="T64">
-        <v>1.633115786144735</v>
+        <v>1.677254050635134</v>
       </c>
       <c r="U64">
         <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.2046206216458946</v>
+        <v>0.201372675270563</v>
       </c>
       <c r="W64">
-        <v>0.09433199427279691</v>
+        <v>0.09471720071291125</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8184824865835785</v>
+        <v>0.8054907010822518</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1075794472248066</v>
+        <v>0.1627570299856732</v>
       </c>
       <c r="C65">
-        <v>-770.5013587368467</v>
+        <v>-4278.466557392962</v>
       </c>
       <c r="D65">
-        <v>7139.950641263154</v>
+        <v>3771.489442607037</v>
       </c>
       <c r="E65">
-        <v>6817.652</v>
+        <v>6957.155999999999</v>
       </c>
       <c r="F65">
-        <v>8788.752</v>
+        <v>8928.255999999999</v>
       </c>
       <c r="G65">
         <v>878.3</v>
@@ -6623,45 +6623,45 @@
         <v>839.6</v>
       </c>
       <c r="M65">
-        <v>1042.3459872</v>
+        <v>1792.7938048</v>
       </c>
       <c r="N65">
-        <v>-202.7459872000001</v>
+        <v>-953.1938047999998</v>
       </c>
       <c r="O65">
-        <v>-50.68649680000001</v>
+        <v>-238.2984512</v>
       </c>
       <c r="P65">
-        <v>-152.0594904</v>
+        <v>-714.8953535999999</v>
       </c>
       <c r="Q65">
-        <v>19.74050959999991</v>
+        <v>-543.0953536</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1294800291234393</v>
+        <v>0.136919982045942</v>
       </c>
       <c r="T65">
-        <v>1.677254050635134</v>
+        <v>1.826377937260396</v>
       </c>
       <c r="U65">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.201372675270563</v>
+        <v>0.11707983340751</v>
       </c>
       <c r="W65">
-        <v>0.09471720071291125</v>
+        <v>0.177290369451772</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8054907010822518</v>
+        <v>0.4683193336300401</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1627570299856732</v>
+        <v>0.1643070299856732</v>
       </c>
       <c r="C66">
-        <v>-4278.466557392962</v>
+        <v>-4467.299349421147</v>
       </c>
       <c r="D66">
-        <v>3771.489442607037</v>
+        <v>3722.160650578854</v>
       </c>
       <c r="E66">
-        <v>6957.155999999999</v>
+        <v>7096.66</v>
       </c>
       <c r="F66">
-        <v>8928.255999999999</v>
+        <v>9067.76</v>
       </c>
       <c r="G66">
         <v>878.3</v>
@@ -6705,37 +6705,37 @@
         <v>839.6</v>
       </c>
       <c r="M66">
-        <v>1792.7938048</v>
+        <v>1820.806208</v>
       </c>
       <c r="N66">
-        <v>-953.1938047999998</v>
+        <v>-981.2062080000002</v>
       </c>
       <c r="O66">
-        <v>-238.2984512</v>
+        <v>-245.301552</v>
       </c>
       <c r="P66">
-        <v>-714.8953535999999</v>
+        <v>-735.9046560000002</v>
       </c>
       <c r="Q66">
-        <v>-543.0953536</v>
+        <v>-564.1046560000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.136919982045942</v>
+        <v>0.1395234101043974</v>
       </c>
       <c r="T66">
-        <v>1.826377937260396</v>
+        <v>1.878560164039264</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.11707983340751</v>
+        <v>0.1152786052012406</v>
       </c>
       <c r="W66">
-        <v>0.177290369451772</v>
+        <v>0.1776520560755909</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4683193336300401</v>
+        <v>0.4611144208049625</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1643070299856732</v>
+        <v>0.1658570299856732</v>
       </c>
       <c r="C67">
-        <v>-4467.299349421147</v>
+        <v>-4654.858419658065</v>
       </c>
       <c r="D67">
-        <v>3722.160650578854</v>
+        <v>3674.105580341936</v>
       </c>
       <c r="E67">
-        <v>7096.66</v>
+        <v>7236.164000000001</v>
       </c>
       <c r="F67">
-        <v>9067.76</v>
+        <v>9207.264000000001</v>
       </c>
       <c r="G67">
         <v>878.3</v>
@@ -6787,37 +6787,37 @@
         <v>839.6</v>
       </c>
       <c r="M67">
-        <v>1820.806208</v>
+        <v>1848.8186112</v>
       </c>
       <c r="N67">
-        <v>-981.2062080000002</v>
+        <v>-1009.2186112</v>
       </c>
       <c r="O67">
-        <v>-245.301552</v>
+        <v>-252.3046528000001</v>
       </c>
       <c r="P67">
-        <v>-735.9046560000002</v>
+        <v>-756.9139584000002</v>
       </c>
       <c r="Q67">
-        <v>-564.1046560000002</v>
+        <v>-585.1139584000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1395234101043974</v>
+        <v>0.1422799809898209</v>
       </c>
       <c r="T67">
-        <v>1.878560164039264</v>
+        <v>1.933811933569831</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1152786052012406</v>
+        <v>0.1135319596678885</v>
       </c>
       <c r="W67">
-        <v>0.1776520560755909</v>
+        <v>0.178002782498688</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4611144208049625</v>
+        <v>0.4541278386715538</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1658570299856732</v>
+        <v>0.1674070299856732</v>
       </c>
       <c r="C68">
-        <v>-4654.858419658065</v>
+        <v>-4841.192472576888</v>
       </c>
       <c r="D68">
-        <v>3674.105580341936</v>
+        <v>3627.275527423113</v>
       </c>
       <c r="E68">
-        <v>7236.164000000001</v>
+        <v>7375.668</v>
       </c>
       <c r="F68">
-        <v>9207.264000000001</v>
+        <v>9346.768</v>
       </c>
       <c r="G68">
         <v>878.3</v>
@@ -6869,37 +6869,37 @@
         <v>839.6</v>
       </c>
       <c r="M68">
-        <v>1848.8186112</v>
+        <v>1876.8310144</v>
       </c>
       <c r="N68">
-        <v>-1009.2186112</v>
+        <v>-1037.2310144</v>
       </c>
       <c r="O68">
-        <v>-252.3046528000001</v>
+        <v>-259.3077536</v>
       </c>
       <c r="P68">
-        <v>-756.9139584000002</v>
+        <v>-777.9232607999999</v>
       </c>
       <c r="Q68">
-        <v>-585.1139584000002</v>
+        <v>-606.1232607999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1422799809898209</v>
+        <v>0.1452036167773912</v>
       </c>
       <c r="T68">
-        <v>1.933811933569831</v>
+        <v>1.992412295193159</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1135319596678885</v>
+        <v>0.1118374528071737</v>
       </c>
       <c r="W68">
-        <v>0.178002782498688</v>
+        <v>0.1783430394763195</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4541278386715538</v>
+        <v>0.447349811228695</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1674070299856732</v>
+        <v>0.1689570299856732</v>
       </c>
       <c r="C69">
-        <v>-4841.192472576888</v>
+        <v>-5026.347760758812</v>
       </c>
       <c r="D69">
-        <v>3627.275527423113</v>
+        <v>3581.624239241189</v>
       </c>
       <c r="E69">
-        <v>7375.668</v>
+        <v>7515.172</v>
       </c>
       <c r="F69">
-        <v>9346.768</v>
+        <v>9486.272000000001</v>
       </c>
       <c r="G69">
         <v>878.3</v>
@@ -6951,37 +6951,37 @@
         <v>839.6</v>
       </c>
       <c r="M69">
-        <v>1876.8310144</v>
+        <v>1904.8434176</v>
       </c>
       <c r="N69">
-        <v>-1037.2310144</v>
+        <v>-1065.2434176</v>
       </c>
       <c r="O69">
-        <v>-259.3077536</v>
+        <v>-266.3108544</v>
       </c>
       <c r="P69">
-        <v>-777.9232607999999</v>
+        <v>-798.9325632000001</v>
       </c>
       <c r="Q69">
-        <v>-606.1232607999999</v>
+        <v>-627.1325632000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1452036167773912</v>
+        <v>0.1483099798016847</v>
       </c>
       <c r="T69">
-        <v>1.992412295193159</v>
+        <v>2.054675179417945</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1118374528071737</v>
+        <v>0.1101927843835388</v>
       </c>
       <c r="W69">
-        <v>0.1783430394763195</v>
+        <v>0.1786732888957854</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.447349811228695</v>
+        <v>0.4407711375341553</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1689570299856732</v>
+        <v>0.1705070299856732</v>
       </c>
       <c r="C70">
-        <v>-5026.347760758812</v>
+        <v>-5210.368237267485</v>
       </c>
       <c r="D70">
-        <v>3581.624239241189</v>
+        <v>3537.107762732515</v>
       </c>
       <c r="E70">
-        <v>7515.172</v>
+        <v>7654.675999999999</v>
       </c>
       <c r="F70">
-        <v>9486.272000000001</v>
+        <v>9625.776</v>
       </c>
       <c r="G70">
         <v>878.3</v>
@@ -7033,37 +7033,37 @@
         <v>839.6</v>
       </c>
       <c r="M70">
-        <v>1904.8434176</v>
+        <v>1932.8558208</v>
       </c>
       <c r="N70">
-        <v>-1065.2434176</v>
+        <v>-1093.2558208</v>
       </c>
       <c r="O70">
-        <v>-266.3108544</v>
+        <v>-273.3139552</v>
       </c>
       <c r="P70">
-        <v>-798.9325632000001</v>
+        <v>-819.9418656</v>
       </c>
       <c r="Q70">
-        <v>-627.1325632000002</v>
+        <v>-648.1418656000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1483099798016847</v>
+        <v>0.1516167533436746</v>
       </c>
       <c r="T70">
-        <v>2.054675179417945</v>
+        <v>2.120955023915299</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1101927843835388</v>
+        <v>0.1085957875084151</v>
       </c>
       <c r="W70">
-        <v>0.1786732888957854</v>
+        <v>0.1789939658683103</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4407711375341553</v>
+        <v>0.4343831500336602</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1705070299856732</v>
+        <v>0.1720570299856732</v>
       </c>
       <c r="C71">
-        <v>-5210.368237267485</v>
+        <v>-5393.295696799662</v>
       </c>
       <c r="D71">
-        <v>3537.107762732515</v>
+        <v>3493.684303200339</v>
       </c>
       <c r="E71">
-        <v>7654.675999999999</v>
+        <v>7794.18</v>
       </c>
       <c r="F71">
-        <v>9625.776</v>
+        <v>9765.280000000001</v>
       </c>
       <c r="G71">
         <v>878.3</v>
@@ -7115,37 +7115,37 @@
         <v>839.6</v>
       </c>
       <c r="M71">
-        <v>1932.8558208</v>
+        <v>1960.868224</v>
       </c>
       <c r="N71">
-        <v>-1093.2558208</v>
+        <v>-1121.268224</v>
       </c>
       <c r="O71">
-        <v>-273.3139552</v>
+        <v>-280.3170560000001</v>
       </c>
       <c r="P71">
-        <v>-819.9418656</v>
+        <v>-840.9511680000003</v>
       </c>
       <c r="Q71">
-        <v>-648.1418656000001</v>
+        <v>-669.1511680000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1516167533436746</v>
+        <v>0.1551439784551304</v>
       </c>
       <c r="T71">
-        <v>2.120955023915299</v>
+        <v>2.191653524712475</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1085957875084151</v>
+        <v>0.1070444191154377</v>
       </c>
       <c r="W71">
-        <v>0.1789939658683103</v>
+        <v>0.1793054806416201</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4343831500336602</v>
+        <v>0.4281776764617508</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1720570299856732</v>
+        <v>0.1736070299856732</v>
       </c>
       <c r="C72">
-        <v>-5393.295696799662</v>
+        <v>-5575.169906564864</v>
       </c>
       <c r="D72">
-        <v>3493.684303200339</v>
+        <v>3451.314093435138</v>
       </c>
       <c r="E72">
-        <v>7794.18</v>
+        <v>7933.684000000001</v>
       </c>
       <c r="F72">
-        <v>9765.280000000001</v>
+        <v>9904.784000000001</v>
       </c>
       <c r="G72">
         <v>878.3</v>
@@ -7197,37 +7197,37 @@
         <v>839.6</v>
       </c>
       <c r="M72">
-        <v>1960.868224</v>
+        <v>1988.8806272</v>
       </c>
       <c r="N72">
-        <v>-1121.268224</v>
+        <v>-1149.2806272</v>
       </c>
       <c r="O72">
-        <v>-280.3170560000001</v>
+        <v>-287.3201568000001</v>
       </c>
       <c r="P72">
-        <v>-840.9511680000003</v>
+        <v>-861.9604704000002</v>
       </c>
       <c r="Q72">
-        <v>-669.1511680000003</v>
+        <v>-690.1604704000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1551439784551304</v>
+        <v>0.1589144604708245</v>
       </c>
       <c r="T72">
-        <v>2.191653524712475</v>
+        <v>2.267227784185319</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1070444191154377</v>
+        <v>0.1055367512405724</v>
       </c>
       <c r="W72">
-        <v>0.1793054806416201</v>
+        <v>0.1796082203508931</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4281776764617508</v>
+        <v>0.4221470049622895</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1736070299856732</v>
+        <v>0.1751570299856732</v>
       </c>
       <c r="C73">
-        <v>-5575.169906564864</v>
+        <v>-5756.028727755614</v>
       </c>
       <c r="D73">
-        <v>3451.314093435136</v>
+        <v>3409.959272244384</v>
       </c>
       <c r="E73">
-        <v>7933.683999999999</v>
+        <v>8073.187999999998</v>
       </c>
       <c r="F73">
-        <v>9904.784</v>
+        <v>10044.288</v>
       </c>
       <c r="G73">
         <v>878.3</v>
@@ -7279,37 +7279,37 @@
         <v>839.6</v>
       </c>
       <c r="M73">
-        <v>1988.8806272</v>
+        <v>2016.8930304</v>
       </c>
       <c r="N73">
-        <v>-1149.2806272</v>
+        <v>-1177.2930304</v>
       </c>
       <c r="O73">
-        <v>-287.3201567999999</v>
+        <v>-294.3232575999999</v>
       </c>
       <c r="P73">
-        <v>-861.9604703999998</v>
+        <v>-882.9697727999998</v>
       </c>
       <c r="Q73">
-        <v>-690.1604703999999</v>
+        <v>-711.1697727999998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1589144604708245</v>
+        <v>0.1629542626304968</v>
       </c>
       <c r="T73">
-        <v>2.267227784185319</v>
+        <v>2.34820020504908</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1055367512405724</v>
+        <v>0.1040709630288978</v>
       </c>
       <c r="W73">
-        <v>0.1796082203508931</v>
+        <v>0.1799025506237973</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4221470049622896</v>
+        <v>0.4162838521155913</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1751570299856732</v>
+        <v>0.1767070299856732</v>
       </c>
       <c r="C74">
-        <v>-5756.028727755614</v>
+        <v>-5935.908228388067</v>
       </c>
       <c r="D74">
-        <v>3409.959272244384</v>
+        <v>3369.583771611933</v>
       </c>
       <c r="E74">
-        <v>8073.187999999998</v>
+        <v>8212.691999999999</v>
       </c>
       <c r="F74">
-        <v>10044.288</v>
+        <v>10183.792</v>
       </c>
       <c r="G74">
         <v>878.3</v>
@@ -7361,37 +7361,37 @@
         <v>839.6</v>
       </c>
       <c r="M74">
-        <v>2016.8930304</v>
+        <v>2044.9054336</v>
       </c>
       <c r="N74">
-        <v>-1177.2930304</v>
+        <v>-1205.3054336</v>
       </c>
       <c r="O74">
-        <v>-294.3232575999999</v>
+        <v>-301.3263584</v>
       </c>
       <c r="P74">
-        <v>-882.9697727999998</v>
+        <v>-903.9790752</v>
       </c>
       <c r="Q74">
-        <v>-711.1697727999998</v>
+        <v>-732.1790752000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1629542626304968</v>
+        <v>0.1672933093945893</v>
       </c>
       <c r="T74">
-        <v>2.34820020504908</v>
+        <v>2.435170583013861</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1040709630288978</v>
+        <v>0.1026453333983649</v>
       </c>
       <c r="W74">
-        <v>0.1799025506237973</v>
+        <v>0.1801888170536083</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4162838521155913</v>
+        <v>0.4105813335934597</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1767070299856732</v>
+        <v>0.1782570299856732</v>
       </c>
       <c r="C75">
-        <v>-5935.908228388067</v>
+        <v>-6114.842788219912</v>
       </c>
       <c r="D75">
-        <v>3369.583771611933</v>
+        <v>3330.153211780088</v>
       </c>
       <c r="E75">
-        <v>8212.691999999999</v>
+        <v>8352.196</v>
       </c>
       <c r="F75">
-        <v>10183.792</v>
+        <v>10323.296</v>
       </c>
       <c r="G75">
         <v>878.3</v>
@@ -7443,37 +7443,37 @@
         <v>839.6</v>
       </c>
       <c r="M75">
-        <v>2044.9054336</v>
+        <v>2072.9178368</v>
       </c>
       <c r="N75">
-        <v>-1205.3054336</v>
+        <v>-1233.3178368</v>
       </c>
       <c r="O75">
-        <v>-301.3263584</v>
+        <v>-308.3294592000001</v>
       </c>
       <c r="P75">
-        <v>-903.9790752</v>
+        <v>-924.9883776000003</v>
       </c>
       <c r="Q75">
-        <v>-732.1790752000001</v>
+        <v>-753.1883776000003</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1672933093945893</v>
+        <v>0.1719661289866889</v>
       </c>
       <c r="T75">
-        <v>2.435170583013861</v>
+        <v>2.528830990052855</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1026453333983649</v>
+        <v>0.101258234298387</v>
       </c>
       <c r="W75">
-        <v>0.1801888170536083</v>
+        <v>0.1804673465528839</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4105813335934597</v>
+        <v>0.405032937193548</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1782570299856732</v>
+        <v>0.1798070299856732</v>
       </c>
       <c r="C76">
-        <v>-6114.842788219912</v>
+        <v>-6292.865196387087</v>
       </c>
       <c r="D76">
-        <v>3330.153211780088</v>
+        <v>3291.634803612912</v>
       </c>
       <c r="E76">
-        <v>8352.196</v>
+        <v>8491.699999999999</v>
       </c>
       <c r="F76">
-        <v>10323.296</v>
+        <v>10462.8</v>
       </c>
       <c r="G76">
         <v>878.3</v>
@@ -7525,37 +7525,37 @@
         <v>839.6</v>
       </c>
       <c r="M76">
-        <v>2072.9178368</v>
+        <v>2100.93024</v>
       </c>
       <c r="N76">
-        <v>-1233.3178368</v>
+        <v>-1261.33024</v>
       </c>
       <c r="O76">
-        <v>-308.3294592000001</v>
+        <v>-315.3325600000001</v>
       </c>
       <c r="P76">
-        <v>-924.9883776000003</v>
+        <v>-945.9976800000002</v>
       </c>
       <c r="Q76">
-        <v>-753.1883776000003</v>
+        <v>-774.1976800000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1719661289866889</v>
+        <v>0.1770127741461564</v>
       </c>
       <c r="T76">
-        <v>2.528830990052855</v>
+        <v>2.62998422965497</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.101258234298387</v>
+        <v>0.09990812450774186</v>
       </c>
       <c r="W76">
-        <v>0.1804673465528839</v>
+        <v>0.1807384485988454</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.405032937193548</v>
+        <v>0.3996324980309673</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1798070299856732</v>
+        <v>0.1813570299856732</v>
       </c>
       <c r="C77">
-        <v>-6292.865196387087</v>
+        <v>-6470.006742342021</v>
       </c>
       <c r="D77">
-        <v>3291.634803612912</v>
+        <v>3253.99725765798</v>
       </c>
       <c r="E77">
-        <v>8491.699999999999</v>
+        <v>8631.204</v>
       </c>
       <c r="F77">
-        <v>10462.8</v>
+        <v>10602.304</v>
       </c>
       <c r="G77">
         <v>878.3</v>
@@ -7607,37 +7607,37 @@
         <v>839.6</v>
       </c>
       <c r="M77">
-        <v>2100.93024</v>
+        <v>2128.9426432</v>
       </c>
       <c r="N77">
-        <v>-1261.33024</v>
+        <v>-1289.3426432</v>
       </c>
       <c r="O77">
-        <v>-315.3325600000001</v>
+        <v>-322.3356608</v>
       </c>
       <c r="P77">
-        <v>-945.9976800000002</v>
+        <v>-967.0069824000001</v>
       </c>
       <c r="Q77">
-        <v>-774.1976800000002</v>
+        <v>-795.2069824000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1770127741461564</v>
+        <v>0.1824799730689129</v>
       </c>
       <c r="T77">
-        <v>2.62998422965497</v>
+        <v>2.739566905890594</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.09990812450774186</v>
+        <v>0.09859354392211368</v>
       </c>
       <c r="W77">
-        <v>0.1807384485988454</v>
+        <v>0.1810024163804396</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3996324980309673</v>
+        <v>0.3943741756884547</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1813570299856732</v>
+        <v>0.1829070299856732</v>
       </c>
       <c r="C78">
-        <v>-6470.006742342021</v>
+        <v>-6646.297300623509</v>
       </c>
       <c r="D78">
-        <v>3253.99725765798</v>
+        <v>3217.210699376491</v>
       </c>
       <c r="E78">
-        <v>8631.204</v>
+        <v>8770.707999999999</v>
       </c>
       <c r="F78">
-        <v>10602.304</v>
+        <v>10741.808</v>
       </c>
       <c r="G78">
         <v>878.3</v>
@@ -7689,37 +7689,37 @@
         <v>839.6</v>
       </c>
       <c r="M78">
-        <v>2128.9426432</v>
+        <v>2156.9550464</v>
       </c>
       <c r="N78">
-        <v>-1289.3426432</v>
+        <v>-1317.3550464</v>
       </c>
       <c r="O78">
-        <v>-322.3356608</v>
+        <v>-329.3387616</v>
       </c>
       <c r="P78">
-        <v>-967.0069824000001</v>
+        <v>-988.0162848</v>
       </c>
       <c r="Q78">
-        <v>-795.2069824000001</v>
+        <v>-816.2162848</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1824799730689129</v>
+        <v>0.1884225805936483</v>
       </c>
       <c r="T78">
-        <v>2.739566905890594</v>
+        <v>2.858678510494533</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.09859354392211368</v>
+        <v>0.09731310828676157</v>
       </c>
       <c r="W78">
-        <v>0.1810024163804396</v>
+        <v>0.1812595278560183</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3943741756884547</v>
+        <v>0.3892524331470462</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1829070299856732</v>
+        <v>0.1844570299856732</v>
       </c>
       <c r="C79">
-        <v>-6646.297300623509</v>
+        <v>-6821.76540994093</v>
       </c>
       <c r="D79">
-        <v>3217.210699376491</v>
+        <v>3181.24659005907</v>
       </c>
       <c r="E79">
-        <v>8770.707999999999</v>
+        <v>8910.212</v>
       </c>
       <c r="F79">
-        <v>10741.808</v>
+        <v>10881.312</v>
       </c>
       <c r="G79">
         <v>878.3</v>
@@ -7771,37 +7771,37 @@
         <v>839.6</v>
       </c>
       <c r="M79">
-        <v>2156.9550464</v>
+        <v>2184.9674496</v>
       </c>
       <c r="N79">
-        <v>-1317.3550464</v>
+        <v>-1345.3674496</v>
       </c>
       <c r="O79">
-        <v>-329.3387616</v>
+        <v>-336.3418624000001</v>
       </c>
       <c r="P79">
-        <v>-988.0162848</v>
+        <v>-1009.0255872</v>
       </c>
       <c r="Q79">
-        <v>-816.2162848</v>
+        <v>-837.2255872000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1884225805936483</v>
+        <v>0.1949054251660869</v>
       </c>
       <c r="T79">
-        <v>2.858678510494533</v>
+        <v>2.988618442789738</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.09731310828676157</v>
+        <v>0.09606550433436717</v>
       </c>
       <c r="W79">
-        <v>0.1812595278560183</v>
+        <v>0.1815100467296591</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3892524331470462</v>
+        <v>0.3842620173374687</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1844570299856732</v>
+        <v>0.1860070299856732</v>
       </c>
       <c r="C80">
-        <v>-6821.76540994093</v>
+        <v>-6996.438347012742</v>
       </c>
       <c r="D80">
-        <v>3181.24659005907</v>
+        <v>3146.077652987259</v>
       </c>
       <c r="E80">
-        <v>8910.212</v>
+        <v>9049.716</v>
       </c>
       <c r="F80">
-        <v>10881.312</v>
+        <v>11020.816</v>
       </c>
       <c r="G80">
         <v>878.3</v>
@@ -7853,37 +7853,37 @@
         <v>839.6</v>
       </c>
       <c r="M80">
-        <v>2184.9674496</v>
+        <v>2212.9798528</v>
       </c>
       <c r="N80">
-        <v>-1345.3674496</v>
+        <v>-1373.3798528</v>
       </c>
       <c r="O80">
-        <v>-336.3418624000001</v>
+        <v>-343.3449632000001</v>
       </c>
       <c r="P80">
-        <v>-1009.0255872</v>
+        <v>-1030.0348896</v>
       </c>
       <c r="Q80">
-        <v>-837.2255872000003</v>
+        <v>-858.2348896000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1949054251660869</v>
+        <v>0.2020056835073291</v>
       </c>
       <c r="T80">
-        <v>2.988618442789738</v>
+        <v>3.130933606732107</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.09606550433436717</v>
+        <v>0.09484948529216</v>
       </c>
       <c r="W80">
-        <v>0.1815100467296591</v>
+        <v>0.1817542233533343</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3842620173374687</v>
+        <v>0.3793979411686399</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1860070299856732</v>
+        <v>0.1875570299856732</v>
       </c>
       <c r="C81">
-        <v>-6996.438347012742</v>
+        <v>-7170.342195560802</v>
       </c>
       <c r="D81">
-        <v>3146.077652987259</v>
+        <v>3111.677804439198</v>
       </c>
       <c r="E81">
-        <v>9049.716</v>
+        <v>9189.219999999999</v>
       </c>
       <c r="F81">
-        <v>11020.816</v>
+        <v>11160.32</v>
       </c>
       <c r="G81">
         <v>878.3</v>
@@ -7935,37 +7935,37 @@
         <v>839.6</v>
       </c>
       <c r="M81">
-        <v>2212.9798528</v>
+        <v>2240.992256</v>
       </c>
       <c r="N81">
-        <v>-1373.3798528</v>
+        <v>-1401.392256</v>
       </c>
       <c r="O81">
-        <v>-343.3449632000001</v>
+        <v>-350.348064</v>
       </c>
       <c r="P81">
-        <v>-1030.0348896</v>
+        <v>-1051.044192</v>
       </c>
       <c r="Q81">
-        <v>-858.2348896000001</v>
+        <v>-879.2441920000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2020056835073291</v>
+        <v>0.2098159676826956</v>
       </c>
       <c r="T81">
-        <v>3.130933606732107</v>
+        <v>3.287480287068713</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.09484948529216</v>
+        <v>0.093663866726008</v>
       </c>
       <c r="W81">
-        <v>0.1817542233533343</v>
+        <v>0.1819922955614176</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3793979411686399</v>
+        <v>0.374655466904032</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1875570299856732</v>
+        <v>0.1891070299856732</v>
       </c>
       <c r="C82">
-        <v>-7170.342195560802</v>
+        <v>-7343.501910827269</v>
       </c>
       <c r="D82">
-        <v>3111.677804439198</v>
+        <v>3078.022089172731</v>
       </c>
       <c r="E82">
-        <v>9189.219999999999</v>
+        <v>9328.724</v>
       </c>
       <c r="F82">
-        <v>11160.32</v>
+        <v>11299.824</v>
       </c>
       <c r="G82">
         <v>878.3</v>
@@ -8017,37 +8017,37 @@
         <v>839.6</v>
       </c>
       <c r="M82">
-        <v>2240.992256</v>
+        <v>2269.0046592</v>
       </c>
       <c r="N82">
-        <v>-1401.392256</v>
+        <v>-1429.4046592</v>
       </c>
       <c r="O82">
-        <v>-350.348064</v>
+        <v>-357.3511648000001</v>
       </c>
       <c r="P82">
-        <v>-1051.044192</v>
+        <v>-1072.0534944</v>
       </c>
       <c r="Q82">
-        <v>-879.2441920000001</v>
+        <v>-900.2534944000004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2098159676826956</v>
+        <v>0.2184483870344164</v>
       </c>
       <c r="T82">
-        <v>3.287480287068713</v>
+        <v>3.460505565335488</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.093663866726008</v>
+        <v>0.09250752269235357</v>
       </c>
       <c r="W82">
-        <v>0.1819922955614176</v>
+        <v>0.1822244894433754</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.374655466904032</v>
+        <v>0.3700300907694142</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1891070299856732</v>
+        <v>0.1906570299856732</v>
       </c>
       <c r="C83">
-        <v>-7343.501910827269</v>
+        <v>-7515.941379949408</v>
       </c>
       <c r="D83">
-        <v>3078.022089172731</v>
+        <v>3045.086620050594</v>
       </c>
       <c r="E83">
-        <v>9328.724</v>
+        <v>9468.228000000001</v>
       </c>
       <c r="F83">
-        <v>11299.824</v>
+        <v>11439.328</v>
       </c>
       <c r="G83">
         <v>878.3</v>
@@ -8099,37 +8099,37 @@
         <v>839.6</v>
       </c>
       <c r="M83">
-        <v>2269.0046592</v>
+        <v>2297.0170624</v>
       </c>
       <c r="N83">
-        <v>-1429.4046592</v>
+        <v>-1457.4170624</v>
       </c>
       <c r="O83">
-        <v>-357.3511648000001</v>
+        <v>-364.3542656000001</v>
       </c>
       <c r="P83">
-        <v>-1072.0534944</v>
+        <v>-1093.0627968</v>
       </c>
       <c r="Q83">
-        <v>-900.2534944000004</v>
+        <v>-921.2627968000004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2184483870344164</v>
+        <v>0.228039964091884</v>
       </c>
       <c r="T83">
-        <v>3.460505565335488</v>
+        <v>3.652755874520792</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.09250752269235357</v>
+        <v>0.09137938217171511</v>
       </c>
       <c r="W83">
-        <v>0.1822244894433754</v>
+        <v>0.1824510200599196</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3700300907694142</v>
+        <v>0.3655175286868604</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1906570299856732</v>
+        <v>0.1922070299856732</v>
       </c>
       <c r="C84">
-        <v>-7515.941379949408</v>
+        <v>-7687.683478499321</v>
       </c>
       <c r="D84">
-        <v>3045.086620050594</v>
+        <v>3012.84852150068</v>
       </c>
       <c r="E84">
-        <v>9468.228000000001</v>
+        <v>9607.732</v>
       </c>
       <c r="F84">
-        <v>11439.328</v>
+        <v>11578.832</v>
       </c>
       <c r="G84">
         <v>878.3</v>
@@ -8181,37 +8181,37 @@
         <v>839.6</v>
       </c>
       <c r="M84">
-        <v>2297.0170624</v>
+        <v>2325.0294656</v>
       </c>
       <c r="N84">
-        <v>-1457.4170624</v>
+        <v>-1485.4294656</v>
       </c>
       <c r="O84">
-        <v>-364.3542656000001</v>
+        <v>-371.3573664</v>
       </c>
       <c r="P84">
-        <v>-1093.0627968</v>
+        <v>-1114.0720992</v>
       </c>
       <c r="Q84">
-        <v>-921.2627968000004</v>
+        <v>-942.2720992000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.228039964091884</v>
+        <v>0.2387599619796419</v>
       </c>
       <c r="T84">
-        <v>3.652755874520792</v>
+        <v>3.867623867139663</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.09137938217171511</v>
+        <v>0.09027842576000771</v>
       </c>
       <c r="W84">
-        <v>0.1824510200599196</v>
+        <v>0.1826720921073905</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3655175286868604</v>
+        <v>0.3611137030400308</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1922070299856732</v>
+        <v>0.1937570299856732</v>
       </c>
       <c r="C85">
-        <v>-7687.683478499321</v>
+        <v>-7858.750123469813</v>
       </c>
       <c r="D85">
-        <v>3012.84852150068</v>
+        <v>2981.285876530188</v>
       </c>
       <c r="E85">
-        <v>9607.732</v>
+        <v>9747.236000000001</v>
       </c>
       <c r="F85">
-        <v>11578.832</v>
+        <v>11718.336</v>
       </c>
       <c r="G85">
         <v>878.3</v>
@@ -8263,37 +8263,37 @@
         <v>839.6</v>
       </c>
       <c r="M85">
-        <v>2325.0294656</v>
+        <v>2353.0418688</v>
       </c>
       <c r="N85">
-        <v>-1485.4294656</v>
+        <v>-1513.441868800001</v>
       </c>
       <c r="O85">
-        <v>-371.3573664</v>
+        <v>-378.3604672000001</v>
       </c>
       <c r="P85">
-        <v>-1114.0720992</v>
+        <v>-1135.0814016</v>
       </c>
       <c r="Q85">
-        <v>-942.2720992000002</v>
+        <v>-963.2814016000004</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2387599619796419</v>
+        <v>0.2508199596033695</v>
       </c>
       <c r="T85">
-        <v>3.867623867139663</v>
+        <v>4.109350358835893</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.09027842576000771</v>
+        <v>0.08920368259619808</v>
       </c>
       <c r="W85">
-        <v>0.1826720921073905</v>
+        <v>0.1828879005346834</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3611137030400308</v>
+        <v>0.3568147303847923</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1937570299856732</v>
+        <v>0.1953070299856732</v>
       </c>
       <c r="C86">
-        <v>-7858.750123469811</v>
+        <v>-8029.162322964276</v>
       </c>
       <c r="D86">
-        <v>2981.285876530188</v>
+        <v>2950.377677035725</v>
       </c>
       <c r="E86">
-        <v>9747.235999999999</v>
+        <v>9886.74</v>
       </c>
       <c r="F86">
-        <v>11718.336</v>
+        <v>11857.84</v>
       </c>
       <c r="G86">
         <v>878.3</v>
@@ -8345,37 +8345,37 @@
         <v>839.6</v>
       </c>
       <c r="M86">
-        <v>2353.0418688</v>
+        <v>2381.054272</v>
       </c>
       <c r="N86">
-        <v>-1513.4418688</v>
+        <v>-1541.454272</v>
       </c>
       <c r="O86">
-        <v>-378.3604672</v>
+        <v>-385.3635680000001</v>
       </c>
       <c r="P86">
-        <v>-1135.0814016</v>
+        <v>-1156.090704</v>
       </c>
       <c r="Q86">
-        <v>-963.2814016</v>
+        <v>-984.2907040000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2508199596033693</v>
+        <v>0.2644879569102607</v>
       </c>
       <c r="T86">
-        <v>4.109350358835889</v>
+        <v>4.383307049424949</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.0892036825961981</v>
+        <v>0.08815422750683105</v>
       </c>
       <c r="W86">
-        <v>0.1828879005346834</v>
+        <v>0.1830986311166283</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3568147303847924</v>
+        <v>0.3526169100273241</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1953070299856732</v>
+        <v>0.1968570299856732</v>
       </c>
       <c r="C87">
-        <v>-8029.162322964276</v>
+        <v>-8198.940222827387</v>
       </c>
       <c r="D87">
-        <v>2950.377677035725</v>
+        <v>2920.103777172614</v>
       </c>
       <c r="E87">
-        <v>9886.74</v>
+        <v>10026.244</v>
       </c>
       <c r="F87">
-        <v>11857.84</v>
+        <v>11997.344</v>
       </c>
       <c r="G87">
         <v>878.3</v>
@@ -8427,37 +8427,37 @@
         <v>839.6</v>
       </c>
       <c r="M87">
-        <v>2381.054272</v>
+        <v>2409.0666752</v>
       </c>
       <c r="N87">
-        <v>-1541.454272</v>
+        <v>-1569.4666752</v>
       </c>
       <c r="O87">
-        <v>-385.3635680000001</v>
+        <v>-392.3666688</v>
       </c>
       <c r="P87">
-        <v>-1156.090704</v>
+        <v>-1177.1000064</v>
       </c>
       <c r="Q87">
-        <v>-984.2907040000002</v>
+        <v>-1005.3000064</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2644879569102607</v>
+        <v>0.2801085252609936</v>
       </c>
       <c r="T87">
-        <v>4.383307049424949</v>
+        <v>4.69640041009816</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08815422750683105</v>
+        <v>0.08712917834977489</v>
       </c>
       <c r="W87">
-        <v>0.1830986311166283</v>
+        <v>0.1833044609873652</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3526169100273241</v>
+        <v>0.3485167133990995</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1968570299856732</v>
+        <v>0.1984070299856732</v>
       </c>
       <c r="C88">
-        <v>-8198.940222827387</v>
+        <v>-8368.103150434079</v>
       </c>
       <c r="D88">
-        <v>2920.103777172614</v>
+        <v>2890.44484956592</v>
       </c>
       <c r="E88">
-        <v>10026.244</v>
+        <v>10165.748</v>
       </c>
       <c r="F88">
-        <v>11997.344</v>
+        <v>12136.848</v>
       </c>
       <c r="G88">
         <v>878.3</v>
@@ -8509,37 +8509,37 @@
         <v>839.6</v>
       </c>
       <c r="M88">
-        <v>2409.0666752</v>
+        <v>2437.0790784</v>
       </c>
       <c r="N88">
-        <v>-1569.4666752</v>
+        <v>-1597.4790784</v>
       </c>
       <c r="O88">
-        <v>-392.3666688</v>
+        <v>-399.3697696</v>
       </c>
       <c r="P88">
-        <v>-1177.1000064</v>
+        <v>-1198.1093088</v>
       </c>
       <c r="Q88">
-        <v>-1005.3000064</v>
+        <v>-1026.3093088</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2801085252609936</v>
+        <v>0.2981322579733777</v>
       </c>
       <c r="T88">
-        <v>4.69640041009816</v>
+        <v>5.057661980105711</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08712917834977489</v>
+        <v>0.08612769354115678</v>
       </c>
       <c r="W88">
-        <v>0.1833044609873652</v>
+        <v>0.1835055591369357</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3485167133990995</v>
+        <v>0.3445107741646271</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1984070299856732</v>
+        <v>0.1999570299856732</v>
       </c>
       <c r="C89">
-        <v>-8368.103150434079</v>
+        <v>-8536.669655836806</v>
       </c>
       <c r="D89">
-        <v>2890.44484956592</v>
+        <v>2861.382344163193</v>
       </c>
       <c r="E89">
-        <v>10165.748</v>
+        <v>10305.252</v>
       </c>
       <c r="F89">
-        <v>12136.848</v>
+        <v>12276.352</v>
       </c>
       <c r="G89">
         <v>878.3</v>
@@ -8591,37 +8591,37 @@
         <v>839.6</v>
       </c>
       <c r="M89">
-        <v>2437.0790784</v>
+        <v>2465.0914816</v>
       </c>
       <c r="N89">
-        <v>-1597.4790784</v>
+        <v>-1625.4914816</v>
       </c>
       <c r="O89">
-        <v>-399.3697696</v>
+        <v>-406.3728704</v>
       </c>
       <c r="P89">
-        <v>-1198.1093088</v>
+        <v>-1219.1186112</v>
       </c>
       <c r="Q89">
-        <v>-1026.3093088</v>
+        <v>-1047.3186112</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2981322579733777</v>
+        <v>0.3191599461378259</v>
       </c>
       <c r="T89">
-        <v>5.057661980105711</v>
+        <v>5.479133811781187</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08612769354115678</v>
+        <v>0.08514896975091636</v>
       </c>
       <c r="W89">
-        <v>0.1835055591369357</v>
+        <v>0.183702086874016</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3445107741646271</v>
+        <v>0.3405958790036654</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1999570299856732</v>
+        <v>0.2015070299856732</v>
       </c>
       <c r="C90">
-        <v>-8536.669655836806</v>
+        <v>-8704.657550455189</v>
       </c>
       <c r="D90">
-        <v>2861.382344163193</v>
+        <v>2832.898449544811</v>
       </c>
       <c r="E90">
-        <v>10305.252</v>
+        <v>10444.756</v>
       </c>
       <c r="F90">
-        <v>12276.352</v>
+        <v>12415.856</v>
       </c>
       <c r="G90">
         <v>878.3</v>
@@ -8673,37 +8673,37 @@
         <v>839.6</v>
       </c>
       <c r="M90">
-        <v>2465.0914816</v>
+        <v>2493.1038848</v>
       </c>
       <c r="N90">
-        <v>-1625.4914816</v>
+        <v>-1653.5038848</v>
       </c>
       <c r="O90">
-        <v>-406.3728704</v>
+        <v>-413.3759712</v>
       </c>
       <c r="P90">
-        <v>-1219.1186112</v>
+        <v>-1240.1279136</v>
       </c>
       <c r="Q90">
-        <v>-1047.3186112</v>
+        <v>-1068.3279136</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3191599461378259</v>
+        <v>0.3440108503321737</v>
       </c>
       <c r="T90">
-        <v>5.479133811781187</v>
+        <v>5.977236885579477</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08514896975091636</v>
+        <v>0.08419223975371506</v>
       </c>
       <c r="W90">
-        <v>0.183702086874016</v>
+        <v>0.183894198257454</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3405958790036654</v>
+        <v>0.3367689590148603</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2015070299856732</v>
+        <v>0.2030570299856732</v>
       </c>
       <c r="C91">
-        <v>-8704.657550455189</v>
+        <v>-8872.083943477584</v>
       </c>
       <c r="D91">
-        <v>2832.898449544811</v>
+        <v>2804.976056522417</v>
       </c>
       <c r="E91">
-        <v>10444.756</v>
+        <v>10584.26</v>
       </c>
       <c r="F91">
-        <v>12415.856</v>
+        <v>12555.36</v>
       </c>
       <c r="G91">
         <v>878.3</v>
@@ -8755,37 +8755,37 @@
         <v>839.6</v>
       </c>
       <c r="M91">
-        <v>2493.1038848</v>
+        <v>2521.116288</v>
       </c>
       <c r="N91">
-        <v>-1653.5038848</v>
+        <v>-1681.516288</v>
       </c>
       <c r="O91">
-        <v>-413.3759712</v>
+        <v>-420.3790720000001</v>
       </c>
       <c r="P91">
-        <v>-1240.1279136</v>
+        <v>-1261.137216</v>
       </c>
       <c r="Q91">
-        <v>-1068.3279136</v>
+        <v>-1089.337216</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3440108503321737</v>
+        <v>0.3738319353653912</v>
       </c>
       <c r="T91">
-        <v>5.977236885579477</v>
+        <v>6.574960574137426</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08419223975371506</v>
+        <v>0.08325677042311821</v>
       </c>
       <c r="W91">
-        <v>0.183894198257454</v>
+        <v>0.1840820404990379</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3367689590148603</v>
+        <v>0.3330270816924729</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2030570299856732</v>
+        <v>0.2046070299856732</v>
       </c>
       <c r="C92">
-        <v>-8872.083943477584</v>
+        <v>-9038.965276130941</v>
       </c>
       <c r="D92">
-        <v>2804.976056522417</v>
+        <v>2777.598723869058</v>
       </c>
       <c r="E92">
-        <v>10584.26</v>
+        <v>10723.764</v>
       </c>
       <c r="F92">
-        <v>12555.36</v>
+        <v>12694.864</v>
       </c>
       <c r="G92">
         <v>878.3</v>
@@ -8837,37 +8837,37 @@
         <v>839.6</v>
       </c>
       <c r="M92">
-        <v>2521.116288</v>
+        <v>2549.1286912</v>
       </c>
       <c r="N92">
-        <v>-1681.516288</v>
+        <v>-1709.5286912</v>
       </c>
       <c r="O92">
-        <v>-420.3790720000001</v>
+        <v>-427.3821728</v>
       </c>
       <c r="P92">
-        <v>-1261.137216</v>
+        <v>-1282.1465184</v>
       </c>
       <c r="Q92">
-        <v>-1089.337216</v>
+        <v>-1110.3465184</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3738319353653912</v>
+        <v>0.4102799281837679</v>
       </c>
       <c r="T92">
-        <v>6.574960574137426</v>
+        <v>7.305511749041584</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08325677042311821</v>
+        <v>0.08234186085802901</v>
       </c>
       <c r="W92">
-        <v>0.1840820404990379</v>
+        <v>0.1842657543397078</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3330270816924729</v>
+        <v>0.329367443432116</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2046070299856732</v>
+        <v>0.2061570299856732</v>
       </c>
       <c r="C93">
-        <v>-9038.965276130941</v>
+        <v>-9205.31735396315</v>
       </c>
       <c r="D93">
-        <v>2777.598723869058</v>
+        <v>2750.75064603685</v>
       </c>
       <c r="E93">
-        <v>10723.764</v>
+        <v>10863.268</v>
       </c>
       <c r="F93">
-        <v>12694.864</v>
+        <v>12834.368</v>
       </c>
       <c r="G93">
         <v>878.3</v>
@@ -8919,37 +8919,37 @@
         <v>839.6</v>
       </c>
       <c r="M93">
-        <v>2549.1286912</v>
+        <v>2577.1410944</v>
       </c>
       <c r="N93">
-        <v>-1709.5286912</v>
+        <v>-1737.5410944</v>
       </c>
       <c r="O93">
-        <v>-427.3821728</v>
+        <v>-434.3852736000001</v>
       </c>
       <c r="P93">
-        <v>-1282.1465184</v>
+        <v>-1303.1558208</v>
       </c>
       <c r="Q93">
-        <v>-1110.3465184</v>
+        <v>-1131.3558208</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4102799281837679</v>
+        <v>0.4558399192067391</v>
       </c>
       <c r="T93">
-        <v>7.305511749041584</v>
+        <v>8.218700717671785</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08234186085802901</v>
+        <v>0.08144684063131129</v>
       </c>
       <c r="W93">
-        <v>0.1842657543397078</v>
+        <v>0.1844454744012327</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.329367443432116</v>
+        <v>0.3257873625252451</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2061570299856732</v>
+        <v>0.2077070299856732</v>
       </c>
       <c r="C94">
-        <v>-9205.31735396315</v>
+        <v>-9371.155377271061</v>
       </c>
       <c r="D94">
-        <v>2750.75064603685</v>
+        <v>2724.41662272894</v>
       </c>
       <c r="E94">
-        <v>10863.268</v>
+        <v>11002.772</v>
       </c>
       <c r="F94">
-        <v>12834.368</v>
+        <v>12973.872</v>
       </c>
       <c r="G94">
         <v>878.3</v>
@@ -9001,37 +9001,37 @@
         <v>839.6</v>
       </c>
       <c r="M94">
-        <v>2577.1410944</v>
+        <v>2605.1534976</v>
       </c>
       <c r="N94">
-        <v>-1737.5410944</v>
+        <v>-1765.5534976</v>
       </c>
       <c r="O94">
-        <v>-434.3852736000001</v>
+        <v>-441.3883744000001</v>
       </c>
       <c r="P94">
-        <v>-1303.1558208</v>
+        <v>-1324.1651232</v>
       </c>
       <c r="Q94">
-        <v>-1131.3558208</v>
+        <v>-1152.3651232</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4558399192067391</v>
+        <v>0.5144170505219875</v>
       </c>
       <c r="T94">
-        <v>8.218700717671785</v>
+        <v>9.392800820196326</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08144684063131129</v>
+        <v>0.08057106815140472</v>
       </c>
       <c r="W94">
-        <v>0.1844454744012327</v>
+        <v>0.1846213295151979</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3257873625252451</v>
+        <v>0.3222842726056189</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2077070299856732</v>
+        <v>0.2092570299856732</v>
       </c>
       <c r="C95">
-        <v>-9371.155377271061</v>
+        <v>-9536.493969797304</v>
       </c>
       <c r="D95">
-        <v>2724.41662272894</v>
+        <v>2698.582030202696</v>
       </c>
       <c r="E95">
-        <v>11002.772</v>
+        <v>11142.276</v>
       </c>
       <c r="F95">
-        <v>12973.872</v>
+        <v>13113.376</v>
       </c>
       <c r="G95">
         <v>878.3</v>
@@ -9083,37 +9083,37 @@
         <v>839.6</v>
       </c>
       <c r="M95">
-        <v>2605.1534976</v>
+        <v>2633.1659008</v>
       </c>
       <c r="N95">
-        <v>-1765.5534976</v>
+        <v>-1793.5659008</v>
       </c>
       <c r="O95">
-        <v>-441.3883744000001</v>
+        <v>-448.3914752000001</v>
       </c>
       <c r="P95">
-        <v>-1324.1651232</v>
+        <v>-1345.1744256</v>
       </c>
       <c r="Q95">
-        <v>-1152.3651232</v>
+        <v>-1173.3744256</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5144170505219875</v>
+        <v>0.5925198922756522</v>
       </c>
       <c r="T95">
-        <v>9.392800820196326</v>
+        <v>10.95826762356238</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08057106815140472</v>
+        <v>0.07971392912851745</v>
       </c>
       <c r="W95">
-        <v>0.1846213295151979</v>
+        <v>0.1847934430309937</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3222842726056189</v>
+        <v>0.3188557165140697</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2092570299856732</v>
+        <v>0.2108070299856732</v>
       </c>
       <c r="C96">
-        <v>-9536.493969797304</v>
+        <v>-9701.347205809718</v>
       </c>
       <c r="D96">
-        <v>2698.582030202696</v>
+        <v>2673.232794190284</v>
       </c>
       <c r="E96">
-        <v>11142.276</v>
+        <v>11281.78</v>
       </c>
       <c r="F96">
-        <v>13113.376</v>
+        <v>13252.88</v>
       </c>
       <c r="G96">
         <v>878.3</v>
@@ -9165,37 +9165,37 @@
         <v>839.6</v>
       </c>
       <c r="M96">
-        <v>2633.1659008</v>
+        <v>2661.178304</v>
       </c>
       <c r="N96">
-        <v>-1793.5659008</v>
+        <v>-1821.578304000001</v>
       </c>
       <c r="O96">
-        <v>-448.3914752000001</v>
+        <v>-455.3945760000001</v>
       </c>
       <c r="P96">
-        <v>-1345.1744256</v>
+        <v>-1366.183728</v>
       </c>
       <c r="Q96">
-        <v>-1173.3744256</v>
+        <v>-1194.383728</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5925198922756522</v>
+        <v>0.7018638707307829</v>
       </c>
       <c r="T96">
-        <v>10.95826762356238</v>
+        <v>13.14992114827487</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.07971392912851745</v>
+        <v>0.07887483513769093</v>
       </c>
       <c r="W96">
-        <v>0.1847934430309937</v>
+        <v>0.1849619331043517</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3188557165140697</v>
+        <v>0.3154993405507637</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2108070299856732</v>
+        <v>0.2123570299856732</v>
       </c>
       <c r="C97">
-        <v>-9701.347205809718</v>
+        <v>-9865.728635668736</v>
       </c>
       <c r="D97">
-        <v>2673.232794190284</v>
+        <v>2648.355364331265</v>
       </c>
       <c r="E97">
-        <v>11281.78</v>
+        <v>11421.284</v>
       </c>
       <c r="F97">
-        <v>13252.88</v>
+        <v>13392.384</v>
       </c>
       <c r="G97">
         <v>878.3</v>
@@ -9247,37 +9247,37 @@
         <v>839.6</v>
       </c>
       <c r="M97">
-        <v>2661.178304</v>
+        <v>2689.1907072</v>
       </c>
       <c r="N97">
-        <v>-1821.578304000001</v>
+        <v>-1849.5907072</v>
       </c>
       <c r="O97">
-        <v>-455.3945760000001</v>
+        <v>-462.3976768</v>
       </c>
       <c r="P97">
-        <v>-1366.183728</v>
+        <v>-1387.1930304</v>
       </c>
       <c r="Q97">
-        <v>-1194.383728</v>
+        <v>-1215.3930304</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7018638707307829</v>
+        <v>0.8658798384134792</v>
       </c>
       <c r="T97">
-        <v>13.14992114827487</v>
+        <v>16.43740143534359</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.07887483513769093</v>
+        <v>0.07805322227167334</v>
       </c>
       <c r="W97">
-        <v>0.1849619331043517</v>
+        <v>0.185126912967848</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3154993405507637</v>
+        <v>0.3122128890866933</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2123570299856732</v>
+        <v>0.2139070299856732</v>
       </c>
       <c r="C98">
-        <v>-9865.728635668736</v>
+        <v>-10029.65130998035</v>
       </c>
       <c r="D98">
-        <v>2648.355364331265</v>
+        <v>2623.936690019648</v>
       </c>
       <c r="E98">
-        <v>11421.284</v>
+        <v>11560.788</v>
       </c>
       <c r="F98">
-        <v>13392.384</v>
+        <v>13531.888</v>
       </c>
       <c r="G98">
         <v>878.3</v>
@@ -9329,37 +9329,37 @@
         <v>839.6</v>
       </c>
       <c r="M98">
-        <v>2689.1907072</v>
+        <v>2717.2031104</v>
       </c>
       <c r="N98">
-        <v>-1849.5907072</v>
+        <v>-1877.6031104</v>
       </c>
       <c r="O98">
-        <v>-462.3976768</v>
+        <v>-469.4007776</v>
       </c>
       <c r="P98">
-        <v>-1387.1930304</v>
+        <v>-1408.2023328</v>
       </c>
       <c r="Q98">
-        <v>-1215.3930304</v>
+        <v>-1236.4023328</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8658798384134769</v>
+        <v>1.139239784551302</v>
       </c>
       <c r="T98">
-        <v>16.43740143534355</v>
+        <v>21.91653524712473</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.07805322227167334</v>
+        <v>0.07724854987712</v>
       </c>
       <c r="W98">
-        <v>0.185126912967848</v>
+        <v>0.1852884911846743</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3122128890866933</v>
+        <v>0.3089941995084799</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2139070299856732</v>
+        <v>0.2154570299856732</v>
       </c>
       <c r="C99">
-        <v>-10029.65130998035</v>
+        <v>-10193.1278024251</v>
       </c>
       <c r="D99">
-        <v>2623.936690019648</v>
+        <v>2599.964197574896</v>
       </c>
       <c r="E99">
-        <v>11560.788</v>
+        <v>11700.292</v>
       </c>
       <c r="F99">
-        <v>13531.888</v>
+        <v>13671.392</v>
       </c>
       <c r="G99">
         <v>878.3</v>
@@ -9411,37 +9411,37 @@
         <v>839.6</v>
       </c>
       <c r="M99">
-        <v>2717.2031104</v>
+        <v>2745.2155136</v>
       </c>
       <c r="N99">
-        <v>-1877.6031104</v>
+        <v>-1905.6155136</v>
       </c>
       <c r="O99">
-        <v>-469.4007776</v>
+        <v>-476.4038784000001</v>
       </c>
       <c r="P99">
-        <v>-1408.2023328</v>
+        <v>-1429.2116352</v>
       </c>
       <c r="Q99">
-        <v>-1236.4023328</v>
+        <v>-1257.4116352</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.139239784551302</v>
+        <v>1.685959676826954</v>
       </c>
       <c r="T99">
-        <v>21.91653524712473</v>
+        <v>32.8748028706871</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.07724854987712</v>
+        <v>0.0764602993681698</v>
       </c>
       <c r="W99">
-        <v>0.1852884911846743</v>
+        <v>0.1854467718868715</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3089941995084799</v>
+        <v>0.3058411974726791</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2154570299856732</v>
+        <v>0.2170070299856732</v>
       </c>
       <c r="C100">
-        <v>-10193.1278024251</v>
+        <v>-10356.17023134697</v>
       </c>
       <c r="D100">
-        <v>2599.964197574896</v>
+        <v>2576.425768653034</v>
       </c>
       <c r="E100">
-        <v>11700.292</v>
+        <v>11839.796</v>
       </c>
       <c r="F100">
-        <v>13671.392</v>
+        <v>13810.896</v>
       </c>
       <c r="G100">
         <v>878.3</v>
@@ -9493,37 +9493,37 @@
         <v>839.6</v>
       </c>
       <c r="M100">
-        <v>2745.2155136</v>
+        <v>2773.2279168</v>
       </c>
       <c r="N100">
-        <v>-1905.6155136</v>
+        <v>-1933.6279168</v>
       </c>
       <c r="O100">
-        <v>-476.4038784000001</v>
+        <v>-483.4069792</v>
       </c>
       <c r="P100">
-        <v>-1429.2116352</v>
+        <v>-1450.2209376</v>
       </c>
       <c r="Q100">
-        <v>-1257.4116352</v>
+        <v>-1278.4209376</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.685959676826954</v>
+        <v>3.326119353653908</v>
       </c>
       <c r="T100">
-        <v>32.8748028706871</v>
+        <v>65.7496057413742</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.0764602993681698</v>
+        <v>0.07568797311192565</v>
       </c>
       <c r="W100">
-        <v>0.1854467718868715</v>
+        <v>0.1856018549991253</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3058411974726791</v>
+        <v>0.3027518924477026</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2170070299856732</v>
-      </c>
-      <c r="C101">
-        <v>-10356.17023134697</v>
-      </c>
-      <c r="D101">
-        <v>2576.425768653034</v>
-      </c>
-      <c r="E101">
-        <v>11839.796</v>
-      </c>
-      <c r="F101">
-        <v>13810.896</v>
-      </c>
-      <c r="G101">
-        <v>878.3</v>
-      </c>
-      <c r="H101">
-        <v>11979.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1011.4</v>
-      </c>
-      <c r="K101">
-        <v>171.8</v>
-      </c>
-      <c r="L101">
-        <v>839.6</v>
-      </c>
-      <c r="M101">
-        <v>2773.2279168</v>
-      </c>
-      <c r="N101">
-        <v>-1933.6279168</v>
-      </c>
-      <c r="O101">
-        <v>-483.4069792</v>
-      </c>
-      <c r="P101">
-        <v>-1450.2209376</v>
-      </c>
-      <c r="Q101">
-        <v>-1278.4209376</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.326119353653908</v>
-      </c>
-      <c r="T101">
-        <v>65.7496057413742</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.07568797311192565</v>
-      </c>
-      <c r="W101">
-        <v>0.1856018549991253</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3027518924477026</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
